--- a/research/traditional_assets/database/data/estonia/estonia_utility_water.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_utility_water.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06817339746528586</v>
+        <v>0.06807305067035528</v>
       </c>
       <c r="C2">
-        <v>319.1260613158977</v>
+        <v>317.1618326065605</v>
       </c>
       <c r="D2">
-        <v>312.0260613158977</v>
+        <v>313.4318326065605</v>
       </c>
       <c r="E2">
-        <v>-125.8</v>
+        <v>-122.43</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="G2">
         <v>7.1</v>
@@ -1451,28 +1451,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.169511</v>
       </c>
       <c r="N2">
-        <v>22.95555555555556</v>
+        <v>22.78604455555556</v>
       </c>
       <c r="O2">
-        <v>4.591111111111111</v>
+        <v>4.557208911111111</v>
       </c>
       <c r="P2">
-        <v>18.36444444444444</v>
+        <v>18.22883564444444</v>
       </c>
       <c r="Q2">
-        <v>26.96444444444444</v>
+        <v>26.82883564444444</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06817339746528586</v>
+        <v>0.06835419259631847</v>
       </c>
       <c r="T2">
-        <v>0.4244150824346248</v>
+        <v>0.4278446992623793</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>135.4222177649566</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06807305067035528</v>
+        <v>0.0679727038754247</v>
       </c>
       <c r="C3">
-        <v>317.1618326065605</v>
+        <v>315.2103280687286</v>
       </c>
       <c r="D3">
-        <v>313.4318326065605</v>
+        <v>314.8503280687286</v>
       </c>
       <c r="E3">
-        <v>-122.43</v>
+        <v>-119.06</v>
       </c>
       <c r="F3">
-        <v>3.37</v>
+        <v>6.74</v>
       </c>
       <c r="G3">
         <v>7.1</v>
@@ -1533,28 +1533,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M3">
-        <v>0.169511</v>
+        <v>0.339022</v>
       </c>
       <c r="N3">
-        <v>22.78604455555556</v>
+        <v>22.61653355555556</v>
       </c>
       <c r="O3">
-        <v>4.557208911111111</v>
+        <v>4.523306711111111</v>
       </c>
       <c r="P3">
-        <v>18.22883564444444</v>
+        <v>18.09322684444444</v>
       </c>
       <c r="Q3">
-        <v>26.82883564444444</v>
+        <v>26.69322684444444</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06835419259631847</v>
+        <v>0.06853867742390277</v>
       </c>
       <c r="T3">
-        <v>0.4278446992623793</v>
+        <v>0.4313443082702921</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>135.4222177649566</v>
+        <v>67.7111088824783</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0679727038754247</v>
+        <v>0.06787235708049413</v>
       </c>
       <c r="C4">
-        <v>315.2103280687286</v>
+        <v>313.2717212447865</v>
       </c>
       <c r="D4">
-        <v>314.8503280687286</v>
+        <v>316.2817212447865</v>
       </c>
       <c r="E4">
-        <v>-119.06</v>
+        <v>-115.69</v>
       </c>
       <c r="F4">
-        <v>6.74</v>
+        <v>10.11</v>
       </c>
       <c r="G4">
         <v>7.1</v>
@@ -1615,28 +1615,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M4">
-        <v>0.339022</v>
+        <v>0.5085329999999999</v>
       </c>
       <c r="N4">
-        <v>22.61653355555556</v>
+        <v>22.44702255555556</v>
       </c>
       <c r="O4">
-        <v>4.523306711111111</v>
+        <v>4.489404511111111</v>
       </c>
       <c r="P4">
-        <v>18.09322684444444</v>
+        <v>17.95761804444444</v>
       </c>
       <c r="Q4">
-        <v>26.69322684444444</v>
+        <v>26.55761804444444</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06853867742390277</v>
+        <v>0.06872696606236509</v>
       </c>
       <c r="T4">
-        <v>0.4313443082702921</v>
+        <v>0.434916074164966</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>67.7111088824783</v>
+        <v>45.14073925498554</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06787235708049413</v>
+        <v>0.06777201028556358</v>
       </c>
       <c r="C5">
-        <v>313.2717212447865</v>
+        <v>311.3461888474112</v>
       </c>
       <c r="D5">
-        <v>316.2817212447865</v>
+        <v>317.7261888474112</v>
       </c>
       <c r="E5">
-        <v>-115.69</v>
+        <v>-112.32</v>
       </c>
       <c r="F5">
-        <v>10.11</v>
+        <v>13.48</v>
       </c>
       <c r="G5">
         <v>7.1</v>
@@ -1697,28 +1697,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M5">
-        <v>0.5085329999999999</v>
+        <v>0.678044</v>
       </c>
       <c r="N5">
-        <v>22.44702255555556</v>
+        <v>22.27751155555556</v>
       </c>
       <c r="O5">
-        <v>4.489404511111111</v>
+        <v>4.455502311111111</v>
       </c>
       <c r="P5">
-        <v>17.95761804444444</v>
+        <v>17.82200924444444</v>
       </c>
       <c r="Q5">
-        <v>26.55761804444444</v>
+        <v>26.42200924444444</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06872696606236509</v>
+        <v>0.06891917738079539</v>
       </c>
       <c r="T5">
-        <v>0.434916074164966</v>
+        <v>0.4385622518491123</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>45.14073925498554</v>
+        <v>33.85555444123915</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06777201028556358</v>
+        <v>0.06767166349063299</v>
       </c>
       <c r="C6">
-        <v>311.3461888474112</v>
+        <v>309.4339108322984</v>
       </c>
       <c r="D6">
-        <v>317.7261888474112</v>
+        <v>319.1839108322984</v>
       </c>
       <c r="E6">
-        <v>-112.32</v>
+        <v>-108.95</v>
       </c>
       <c r="F6">
-        <v>13.48</v>
+        <v>16.85</v>
       </c>
       <c r="G6">
         <v>7.1</v>
@@ -1779,28 +1779,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M6">
-        <v>0.678044</v>
+        <v>0.8475550000000001</v>
       </c>
       <c r="N6">
-        <v>22.27751155555556</v>
+        <v>22.10800055555556</v>
       </c>
       <c r="O6">
-        <v>4.455502311111111</v>
+        <v>4.421600111111111</v>
       </c>
       <c r="P6">
-        <v>17.82200924444444</v>
+        <v>17.68640044444444</v>
       </c>
       <c r="Q6">
-        <v>26.42200924444444</v>
+        <v>26.28640044444444</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06891917738079539</v>
+        <v>0.06911543525329789</v>
       </c>
       <c r="T6">
-        <v>0.4385622518491123</v>
+        <v>0.4422851911687142</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.85555444123915</v>
+        <v>27.08444355299132</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06767166349063299</v>
+        <v>0.06757131669570242</v>
       </c>
       <c r="C7">
-        <v>309.4339108322984</v>
+        <v>307.5350704728978</v>
       </c>
       <c r="D7">
-        <v>319.1839108322984</v>
+        <v>320.6550704728978</v>
       </c>
       <c r="E7">
-        <v>-108.95</v>
+        <v>-105.58</v>
       </c>
       <c r="F7">
-        <v>16.85</v>
+        <v>20.22</v>
       </c>
       <c r="G7">
         <v>7.1</v>
@@ -1861,28 +1861,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M7">
-        <v>0.8475550000000001</v>
+        <v>1.017066</v>
       </c>
       <c r="N7">
-        <v>22.10800055555556</v>
+        <v>21.93848955555556</v>
       </c>
       <c r="O7">
-        <v>4.421600111111111</v>
+        <v>4.387697911111111</v>
       </c>
       <c r="P7">
-        <v>17.68640044444444</v>
+        <v>17.55079164444444</v>
       </c>
       <c r="Q7">
-        <v>26.28640044444444</v>
+        <v>26.15079164444444</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06911543525329789</v>
+        <v>0.06931586882521534</v>
       </c>
       <c r="T7">
-        <v>0.4422851911687142</v>
+        <v>0.4460873419632014</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.08444355299132</v>
+        <v>22.57036962749276</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06757131669570242</v>
+        <v>0.06747096990077185</v>
       </c>
       <c r="C8">
-        <v>307.5350704728978</v>
+        <v>305.64985443723</v>
       </c>
       <c r="D8">
-        <v>320.6550704728978</v>
+        <v>322.1398544372299</v>
       </c>
       <c r="E8">
-        <v>-105.58</v>
+        <v>-102.21</v>
       </c>
       <c r="F8">
-        <v>20.22</v>
+        <v>23.59</v>
       </c>
       <c r="G8">
         <v>7.1</v>
@@ -1943,28 +1943,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M8">
-        <v>1.017066</v>
+        <v>1.186577</v>
       </c>
       <c r="N8">
-        <v>21.93848955555556</v>
+        <v>21.76897855555556</v>
       </c>
       <c r="O8">
-        <v>4.387697911111111</v>
+        <v>4.353795711111111</v>
       </c>
       <c r="P8">
-        <v>17.55079164444444</v>
+        <v>17.41518284444444</v>
       </c>
       <c r="Q8">
-        <v>26.15079164444444</v>
+        <v>26.01518284444444</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06931586882521534</v>
+        <v>0.06952061279652888</v>
       </c>
       <c r="T8">
-        <v>0.4460873419632014</v>
+        <v>0.449971259441441</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.57036962749277</v>
+        <v>19.34603110927952</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06747096990077185</v>
+        <v>0.0673706231058413</v>
       </c>
       <c r="C9">
-        <v>305.6498544372299</v>
+        <v>303.7784528668422</v>
       </c>
       <c r="D9">
-        <v>322.1398544372299</v>
+        <v>323.6384528668422</v>
       </c>
       <c r="E9">
-        <v>-102.21</v>
+        <v>-98.84</v>
       </c>
       <c r="F9">
-        <v>23.59</v>
+        <v>26.96</v>
       </c>
       <c r="G9">
         <v>7.1</v>
@@ -2025,28 +2025,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M9">
-        <v>1.186577</v>
+        <v>1.356088</v>
       </c>
       <c r="N9">
-        <v>21.76897855555556</v>
+        <v>21.59946755555556</v>
       </c>
       <c r="O9">
-        <v>4.353795711111111</v>
+        <v>4.319893511111111</v>
       </c>
       <c r="P9">
-        <v>17.41518284444444</v>
+        <v>17.27957404444444</v>
       </c>
       <c r="Q9">
-        <v>26.01518284444444</v>
+        <v>25.87957404444444</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06952061279652888</v>
+        <v>0.06972980772374053</v>
       </c>
       <c r="T9">
-        <v>0.449971259441441</v>
+        <v>0.4539396099083378</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.34603110927951</v>
+        <v>16.92777722061957</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0673706231058413</v>
+        <v>0.06727027631091072</v>
       </c>
       <c r="C10">
-        <v>303.7784528668422</v>
+        <v>301.9210594579822</v>
       </c>
       <c r="D10">
-        <v>323.6384528668422</v>
+        <v>325.1510594579821</v>
       </c>
       <c r="E10">
-        <v>-98.84</v>
+        <v>-95.47</v>
       </c>
       <c r="F10">
-        <v>26.96</v>
+        <v>30.33</v>
       </c>
       <c r="G10">
         <v>7.1</v>
@@ -2107,28 +2107,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M10">
-        <v>1.356088</v>
+        <v>1.525599</v>
       </c>
       <c r="N10">
-        <v>21.59946755555556</v>
+        <v>21.42995655555556</v>
       </c>
       <c r="O10">
-        <v>4.319893511111111</v>
+        <v>4.285991311111111</v>
       </c>
       <c r="P10">
-        <v>17.27957404444444</v>
+        <v>17.14396524444444</v>
       </c>
       <c r="Q10">
-        <v>25.87957404444444</v>
+        <v>25.74396524444444</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.06972980772374053</v>
+        <v>0.06994360034166013</v>
       </c>
       <c r="T10">
-        <v>0.4539396099083378</v>
+        <v>0.4579951768690126</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.92777722061957</v>
+        <v>15.04691308499518</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06727027631091072</v>
+        <v>0.06716992951598015</v>
       </c>
       <c r="C11">
-        <v>301.9210594579822</v>
+        <v>300.0778715450547</v>
       </c>
       <c r="D11">
-        <v>325.1510594579821</v>
+        <v>326.6778715450546</v>
       </c>
       <c r="E11">
-        <v>-95.47</v>
+        <v>-92.09999999999999</v>
       </c>
       <c r="F11">
-        <v>30.33</v>
+        <v>33.7</v>
       </c>
       <c r="G11">
         <v>7.1</v>
@@ -2189,28 +2189,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M11">
-        <v>1.525599</v>
+        <v>1.69511</v>
       </c>
       <c r="N11">
-        <v>21.42995655555556</v>
+        <v>21.26044555555556</v>
       </c>
       <c r="O11">
-        <v>4.285991311111111</v>
+        <v>4.252089111111111</v>
       </c>
       <c r="P11">
-        <v>17.14396524444444</v>
+        <v>17.00835644444444</v>
       </c>
       <c r="Q11">
-        <v>25.74396524444444</v>
+        <v>25.60835644444444</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.06994360034166013</v>
+        <v>0.0701621439066446</v>
       </c>
       <c r="T11">
-        <v>0.4579951768690126</v>
+        <v>0.4621408675399247</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.04691308499518</v>
+        <v>13.54222177649566</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06716992951598015</v>
+        <v>0.06720158272104958</v>
       </c>
       <c r="C12">
-        <v>300.0778715450547</v>
+        <v>296.2247109398584</v>
       </c>
       <c r="D12">
-        <v>326.6778715450546</v>
+        <v>326.1947109398584</v>
       </c>
       <c r="E12">
-        <v>-92.09999999999999</v>
+        <v>-88.72999999999999</v>
       </c>
       <c r="F12">
-        <v>33.7</v>
+        <v>37.07</v>
       </c>
       <c r="G12">
         <v>7.1</v>
@@ -2271,45 +2271,45 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M12">
-        <v>1.69511</v>
+        <v>1.920226</v>
       </c>
       <c r="N12">
-        <v>21.26044555555556</v>
+        <v>21.03532955555556</v>
       </c>
       <c r="O12">
-        <v>4.252089111111111</v>
+        <v>4.207065911111111</v>
       </c>
       <c r="P12">
-        <v>17.00835644444444</v>
+        <v>16.82826364444444</v>
       </c>
       <c r="Q12">
-        <v>25.60835644444444</v>
+        <v>25.42826364444444</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0701621439066446</v>
+        <v>0.07038559856297705</v>
       </c>
       <c r="T12">
-        <v>0.4621408675399248</v>
+        <v>0.4663797197989472</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.54222177649566</v>
+        <v>11.95461136113955</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06720158272104958</v>
+        <v>0.06711323592611901</v>
       </c>
       <c r="C13">
-        <v>296.2247109398584</v>
+        <v>294.2068405430185</v>
       </c>
       <c r="D13">
-        <v>326.1947109398584</v>
+        <v>327.5468405430184</v>
       </c>
       <c r="E13">
-        <v>-88.72999999999999</v>
+        <v>-85.36</v>
       </c>
       <c r="F13">
-        <v>37.07</v>
+        <v>40.44</v>
       </c>
       <c r="G13">
         <v>7.1</v>
@@ -2353,28 +2353,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M13">
-        <v>1.920226</v>
+        <v>2.094792</v>
       </c>
       <c r="N13">
-        <v>21.03532955555556</v>
+        <v>20.86076355555556</v>
       </c>
       <c r="O13">
-        <v>4.207065911111111</v>
+        <v>4.172152711111112</v>
       </c>
       <c r="P13">
-        <v>16.82826364444444</v>
+        <v>16.68861084444445</v>
       </c>
       <c r="Q13">
-        <v>25.42826364444444</v>
+        <v>25.28861084444445</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07038559856297705</v>
+        <v>0.07061413173422613</v>
       </c>
       <c r="T13">
-        <v>0.4663797197989472</v>
+        <v>0.4707149096093111</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.95461136113955</v>
+        <v>10.95839374771126</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06711323592611901</v>
+        <v>0.06702488913118843</v>
       </c>
       <c r="C14">
-        <v>294.2068405430185</v>
+        <v>292.200226395013</v>
       </c>
       <c r="D14">
-        <v>327.5468405430184</v>
+        <v>328.910226395013</v>
       </c>
       <c r="E14">
-        <v>-85.36</v>
+        <v>-81.98999999999999</v>
       </c>
       <c r="F14">
-        <v>40.44</v>
+        <v>43.81</v>
       </c>
       <c r="G14">
         <v>7.1</v>
@@ -2435,28 +2435,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M14">
-        <v>2.094792</v>
+        <v>2.269358</v>
       </c>
       <c r="N14">
-        <v>20.86076355555556</v>
+        <v>20.68619755555556</v>
       </c>
       <c r="O14">
-        <v>4.172152711111112</v>
+        <v>4.137239511111111</v>
       </c>
       <c r="P14">
-        <v>16.68861084444445</v>
+        <v>16.54895804444444</v>
       </c>
       <c r="Q14">
-        <v>25.28861084444445</v>
+        <v>25.14895804444444</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07061413173422613</v>
+        <v>0.07084791854159589</v>
       </c>
       <c r="T14">
-        <v>0.4707149096093111</v>
+        <v>0.4751497589555454</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.95839374771126</v>
+        <v>10.1154403825027</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06702488913118843</v>
+        <v>0.06712694233625785</v>
       </c>
       <c r="C15">
-        <v>292.200226395013</v>
+        <v>287.2563325730817</v>
       </c>
       <c r="D15">
-        <v>328.910226395013</v>
+        <v>327.3363325730817</v>
       </c>
       <c r="E15">
-        <v>-81.98999999999999</v>
+        <v>-78.61999999999999</v>
       </c>
       <c r="F15">
-        <v>43.81</v>
+        <v>47.18000000000001</v>
       </c>
       <c r="G15">
         <v>7.1</v>
@@ -2517,45 +2517,45 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M15">
-        <v>2.269358</v>
+        <v>2.52413</v>
       </c>
       <c r="N15">
-        <v>20.68619755555556</v>
+        <v>20.43142555555556</v>
       </c>
       <c r="O15">
-        <v>4.137239511111111</v>
+        <v>4.086285111111112</v>
       </c>
       <c r="P15">
-        <v>16.54895804444444</v>
+        <v>16.34514044444445</v>
       </c>
       <c r="Q15">
-        <v>25.14895804444444</v>
+        <v>24.94514044444444</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07084791854159589</v>
+        <v>0.07108714225146262</v>
       </c>
       <c r="T15">
-        <v>0.4751497589555454</v>
+        <v>0.4796877443330876</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.1154403825027</v>
+        <v>9.094442661651957</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06712694233625785</v>
+        <v>0.06705219554132728</v>
       </c>
       <c r="C16">
-        <v>287.2563325730817</v>
+        <v>285.0376179391788</v>
       </c>
       <c r="D16">
-        <v>327.3363325730817</v>
+        <v>328.4876179391788</v>
       </c>
       <c r="E16">
-        <v>-78.61999999999999</v>
+        <v>-75.25</v>
       </c>
       <c r="F16">
-        <v>47.18000000000001</v>
+        <v>50.55</v>
       </c>
       <c r="G16">
         <v>7.1</v>
@@ -2599,28 +2599,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M16">
-        <v>2.52413</v>
+        <v>2.704425</v>
       </c>
       <c r="N16">
-        <v>20.43142555555556</v>
+        <v>20.25113055555556</v>
       </c>
       <c r="O16">
-        <v>4.086285111111112</v>
+        <v>4.050226111111111</v>
       </c>
       <c r="P16">
-        <v>16.34514044444445</v>
+        <v>16.20090444444444</v>
       </c>
       <c r="Q16">
-        <v>24.94514044444444</v>
+        <v>24.80090444444444</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07108714225146262</v>
+        <v>0.07133199475450269</v>
       </c>
       <c r="T16">
-        <v>0.4796877443330876</v>
+        <v>0.48433250583716</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.094442661651957</v>
+        <v>8.488146484208492</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06705219554132728</v>
+        <v>0.0669774487463967</v>
       </c>
       <c r="C17">
-        <v>285.0376179391788</v>
+        <v>282.8270303362699</v>
       </c>
       <c r="D17">
-        <v>328.4876179391788</v>
+        <v>329.6470303362699</v>
       </c>
       <c r="E17">
-        <v>-75.25</v>
+        <v>-71.88</v>
       </c>
       <c r="F17">
-        <v>50.55</v>
+        <v>53.92</v>
       </c>
       <c r="G17">
         <v>7.1</v>
@@ -2681,28 +2681,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M17">
-        <v>2.704425</v>
+        <v>2.88472</v>
       </c>
       <c r="N17">
-        <v>20.25113055555556</v>
+        <v>20.07083555555555</v>
       </c>
       <c r="O17">
-        <v>4.050226111111111</v>
+        <v>4.014167111111111</v>
       </c>
       <c r="P17">
-        <v>16.20090444444444</v>
+        <v>16.05666844444444</v>
       </c>
       <c r="Q17">
-        <v>24.80090444444444</v>
+        <v>24.65666844444444</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07133199475450269</v>
+        <v>0.0715826770790437</v>
       </c>
       <c r="T17">
-        <v>0.48433250583716</v>
+        <v>0.4890878569008533</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.488146484208494</v>
+        <v>7.957637328945462</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0669774487463967</v>
+        <v>0.06701150195146613</v>
       </c>
       <c r="C18">
-        <v>282.8270303362699</v>
+        <v>278.9278109556597</v>
       </c>
       <c r="D18">
-        <v>329.6470303362699</v>
+        <v>329.1178109556596</v>
       </c>
       <c r="E18">
-        <v>-71.88</v>
+        <v>-68.50999999999999</v>
       </c>
       <c r="F18">
-        <v>53.92</v>
+        <v>57.29000000000001</v>
       </c>
       <c r="G18">
         <v>7.1</v>
@@ -2763,45 +2763,45 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M18">
-        <v>2.88472</v>
+        <v>3.110847000000001</v>
       </c>
       <c r="N18">
-        <v>20.07083555555555</v>
+        <v>19.84470855555556</v>
       </c>
       <c r="O18">
-        <v>4.014167111111111</v>
+        <v>3.968941711111111</v>
       </c>
       <c r="P18">
-        <v>16.05666844444444</v>
+        <v>15.87576684444445</v>
       </c>
       <c r="Q18">
-        <v>24.65666844444444</v>
+        <v>24.47576684444444</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0715826770790437</v>
+        <v>0.07183939994152547</v>
       </c>
       <c r="T18">
-        <v>0.4890878569008533</v>
+        <v>0.4939577947371657</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.957637328945462</v>
+        <v>7.379197869762014</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06701150195146613</v>
+        <v>0.06694315515653558</v>
       </c>
       <c r="C19">
-        <v>278.9278109556597</v>
+        <v>276.6217083431044</v>
       </c>
       <c r="D19">
-        <v>329.1178109556596</v>
+        <v>330.1817083431044</v>
       </c>
       <c r="E19">
-        <v>-68.50999999999999</v>
+        <v>-65.13999999999999</v>
       </c>
       <c r="F19">
-        <v>57.29000000000001</v>
+        <v>60.66</v>
       </c>
       <c r="G19">
         <v>7.1</v>
@@ -2845,28 +2845,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M19">
-        <v>3.110847000000001</v>
+        <v>3.293838</v>
       </c>
       <c r="N19">
-        <v>19.84470855555556</v>
+        <v>19.66171755555555</v>
       </c>
       <c r="O19">
-        <v>3.968941711111111</v>
+        <v>3.932343511111111</v>
       </c>
       <c r="P19">
-        <v>15.87576684444445</v>
+        <v>15.72937404444444</v>
       </c>
       <c r="Q19">
-        <v>24.47576684444444</v>
+        <v>24.32937404444444</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07183939994152547</v>
+        <v>0.07210238433723851</v>
       </c>
       <c r="T19">
-        <v>0.4939577947371657</v>
+        <v>0.4989465115450956</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.379197869762014</v>
+        <v>6.969242432553014</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06694315515653557</v>
+        <v>0.066874808361605</v>
       </c>
       <c r="C20">
-        <v>276.6217083431046</v>
+        <v>274.3225062892944</v>
       </c>
       <c r="D20">
-        <v>330.1817083431046</v>
+        <v>331.2525062892944</v>
       </c>
       <c r="E20">
-        <v>-65.14</v>
+        <v>-61.77</v>
       </c>
       <c r="F20">
-        <v>60.66</v>
+        <v>64.03</v>
       </c>
       <c r="G20">
         <v>7.1</v>
@@ -2927,28 +2927,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M20">
-        <v>3.293838</v>
+        <v>3.476829</v>
       </c>
       <c r="N20">
-        <v>19.66171755555555</v>
+        <v>19.47872655555556</v>
       </c>
       <c r="O20">
-        <v>3.932343511111111</v>
+        <v>3.895745311111112</v>
       </c>
       <c r="P20">
-        <v>15.72937404444444</v>
+        <v>15.58298124444445</v>
       </c>
       <c r="Q20">
-        <v>24.32937404444444</v>
+        <v>24.18298124444444</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07210238433723849</v>
+        <v>0.07237186217482099</v>
       </c>
       <c r="T20">
-        <v>0.4989465115450955</v>
+        <v>0.5040584065458137</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.969242432553014</v>
+        <v>6.602440199260751</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.066874808361605</v>
+        <v>0.06680646156667441</v>
       </c>
       <c r="C21">
-        <v>274.3225062892944</v>
+        <v>272.0302721493722</v>
       </c>
       <c r="D21">
-        <v>331.2525062892944</v>
+        <v>332.3302721493722</v>
       </c>
       <c r="E21">
-        <v>-61.77</v>
+        <v>-58.39999999999999</v>
       </c>
       <c r="F21">
-        <v>64.03</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="G21">
         <v>7.1</v>
@@ -3009,28 +3009,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M21">
-        <v>3.476829</v>
+        <v>3.65982</v>
       </c>
       <c r="N21">
-        <v>19.47872655555556</v>
+        <v>19.29573555555556</v>
       </c>
       <c r="O21">
-        <v>3.895745311111112</v>
+        <v>3.859147111111112</v>
       </c>
       <c r="P21">
-        <v>15.58298124444445</v>
+        <v>15.43658844444444</v>
       </c>
       <c r="Q21">
-        <v>24.18298124444444</v>
+        <v>24.03658844444444</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07237186217482099</v>
+        <v>0.07264807695834302</v>
       </c>
       <c r="T21">
-        <v>0.5040584065458137</v>
+        <v>0.5092980989215498</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.602440199260751</v>
+        <v>6.272318189297713</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06680646156667441</v>
+        <v>0.06690611477174385</v>
       </c>
       <c r="C22">
-        <v>272.0302721493722</v>
+        <v>267.0911639966192</v>
       </c>
       <c r="D22">
-        <v>332.3302721493722</v>
+        <v>330.7611639966192</v>
       </c>
       <c r="E22">
-        <v>-58.39999999999999</v>
+        <v>-55.02999999999999</v>
       </c>
       <c r="F22">
-        <v>67.40000000000001</v>
+        <v>70.77000000000001</v>
       </c>
       <c r="G22">
         <v>7.1</v>
@@ -3091,45 +3091,45 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M22">
-        <v>3.65982</v>
+        <v>3.913581000000001</v>
       </c>
       <c r="N22">
-        <v>19.29573555555556</v>
+        <v>19.04197455555556</v>
       </c>
       <c r="O22">
-        <v>3.859147111111112</v>
+        <v>3.808394911111111</v>
       </c>
       <c r="P22">
-        <v>15.43658844444444</v>
+        <v>15.23357964444444</v>
       </c>
       <c r="Q22">
-        <v>24.03658844444444</v>
+        <v>23.83357964444444</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07264807695834302</v>
+        <v>0.07293128452119475</v>
       </c>
       <c r="T22">
-        <v>0.5092980989215498</v>
+        <v>0.5146704417371779</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.272318189297713</v>
+        <v>5.865614013241466</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06690611477174385</v>
+        <v>0.06684576797681328</v>
       </c>
       <c r="C23">
-        <v>267.0911639966192</v>
+        <v>264.6695910702567</v>
       </c>
       <c r="D23">
-        <v>330.7611639966192</v>
+        <v>331.7095910702566</v>
       </c>
       <c r="E23">
-        <v>-55.03</v>
+        <v>-51.66</v>
       </c>
       <c r="F23">
-        <v>70.77</v>
+        <v>74.14</v>
       </c>
       <c r="G23">
         <v>7.1</v>
@@ -3173,28 +3173,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M23">
-        <v>3.913581</v>
+        <v>4.099942</v>
       </c>
       <c r="N23">
-        <v>19.04197455555556</v>
+        <v>18.85561355555556</v>
       </c>
       <c r="O23">
-        <v>3.808394911111111</v>
+        <v>3.771122711111111</v>
       </c>
       <c r="P23">
-        <v>15.23357964444444</v>
+        <v>15.08449084444445</v>
       </c>
       <c r="Q23">
-        <v>23.83357964444444</v>
+        <v>23.68449084444444</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07293128452119475</v>
+        <v>0.07322175381642729</v>
       </c>
       <c r="T23">
-        <v>0.5146704417371779</v>
+        <v>0.5201805369326939</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.865614013241467</v>
+        <v>5.598995194457764</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06684576797681328</v>
+        <v>0.06678542118188271</v>
       </c>
       <c r="C24">
-        <v>264.6695910702567</v>
+        <v>262.2534728387151</v>
       </c>
       <c r="D24">
-        <v>331.7095910702566</v>
+        <v>332.6634728387151</v>
       </c>
       <c r="E24">
-        <v>-51.66</v>
+        <v>-48.28999999999999</v>
       </c>
       <c r="F24">
-        <v>74.14</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="G24">
         <v>7.1</v>
@@ -3255,28 +3255,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M24">
-        <v>4.099942</v>
+        <v>4.286303</v>
       </c>
       <c r="N24">
-        <v>18.85561355555556</v>
+        <v>18.66925255555556</v>
       </c>
       <c r="O24">
-        <v>3.771122711111111</v>
+        <v>3.733850511111111</v>
       </c>
       <c r="P24">
-        <v>15.08449084444445</v>
+        <v>14.93540204444444</v>
       </c>
       <c r="Q24">
-        <v>23.68449084444444</v>
+        <v>23.53540204444444</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07322175381642729</v>
+        <v>0.07351976776867884</v>
       </c>
       <c r="T24">
-        <v>0.5201805369326939</v>
+        <v>0.5258337514839377</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.598995194457764</v>
+        <v>5.355560620785687</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06678542118188271</v>
+        <v>0.06672507438695213</v>
       </c>
       <c r="C25">
-        <v>262.2534728387151</v>
+        <v>259.8428564951388</v>
       </c>
       <c r="D25">
-        <v>332.6634728387151</v>
+        <v>333.6228564951388</v>
       </c>
       <c r="E25">
-        <v>-48.28999999999999</v>
+        <v>-44.91999999999999</v>
       </c>
       <c r="F25">
-        <v>77.51000000000001</v>
+        <v>80.88000000000001</v>
       </c>
       <c r="G25">
         <v>7.1</v>
@@ -3337,28 +3337,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M25">
-        <v>4.286303</v>
+        <v>4.472664000000001</v>
       </c>
       <c r="N25">
-        <v>18.66925255555556</v>
+        <v>18.48289155555555</v>
       </c>
       <c r="O25">
-        <v>3.733850511111111</v>
+        <v>3.696578311111111</v>
       </c>
       <c r="P25">
-        <v>14.93540204444444</v>
+        <v>14.78631324444444</v>
       </c>
       <c r="Q25">
-        <v>23.53540204444444</v>
+        <v>23.38631324444444</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07351976776867884</v>
+        <v>0.07382562419335807</v>
       </c>
       <c r="T25">
-        <v>0.5258337514839377</v>
+        <v>0.5316357348391616</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.355560620785687</v>
+        <v>5.132412261586283</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06672507438695213</v>
+        <v>0.06666472759202156</v>
       </c>
       <c r="C26">
-        <v>259.8428564951388</v>
+        <v>257.4377897786561</v>
       </c>
       <c r="D26">
-        <v>333.6228564951388</v>
+        <v>334.5877897786561</v>
       </c>
       <c r="E26">
-        <v>-44.92</v>
+        <v>-41.55</v>
       </c>
       <c r="F26">
-        <v>80.88</v>
+        <v>84.25</v>
       </c>
       <c r="G26">
         <v>7.1</v>
@@ -3419,28 +3419,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M26">
-        <v>4.472664</v>
+        <v>4.659025</v>
       </c>
       <c r="N26">
-        <v>18.48289155555555</v>
+        <v>18.29653055555556</v>
       </c>
       <c r="O26">
-        <v>3.696578311111111</v>
+        <v>3.659306111111111</v>
       </c>
       <c r="P26">
-        <v>14.78631324444444</v>
+        <v>14.63722444444445</v>
       </c>
       <c r="Q26">
-        <v>23.38631324444444</v>
+        <v>23.23722444444444</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07382562419335807</v>
+        <v>0.07413963678936208</v>
       </c>
       <c r="T26">
-        <v>0.5316357348391615</v>
+        <v>0.5375924377505247</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.132412261586284</v>
+        <v>4.927115771122833</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06666472759202156</v>
+        <v>0.06660438079709098</v>
       </c>
       <c r="C27">
-        <v>257.4377897786561</v>
+        <v>255.0383209822992</v>
       </c>
       <c r="D27">
-        <v>334.5877897786561</v>
+        <v>335.5583209822992</v>
       </c>
       <c r="E27">
-        <v>-41.55</v>
+        <v>-38.17999999999999</v>
       </c>
       <c r="F27">
-        <v>84.25</v>
+        <v>87.62</v>
       </c>
       <c r="G27">
         <v>7.1</v>
@@ -3501,28 +3501,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M27">
-        <v>4.659025</v>
+        <v>4.845386</v>
       </c>
       <c r="N27">
-        <v>18.29653055555556</v>
+        <v>18.11016955555555</v>
       </c>
       <c r="O27">
-        <v>3.659306111111111</v>
+        <v>3.622033911111111</v>
       </c>
       <c r="P27">
-        <v>14.63722444444445</v>
+        <v>14.48813564444444</v>
       </c>
       <c r="Q27">
-        <v>23.23722444444444</v>
+        <v>23.08813564444444</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07413963678936208</v>
+        <v>0.07446213621228512</v>
       </c>
       <c r="T27">
-        <v>0.5375924377505247</v>
+        <v>0.5437101326324653</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.927115771122833</v>
+        <v>4.737611318387339</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06660438079709098</v>
+        <v>0.06654403400216043</v>
       </c>
       <c r="C28">
-        <v>255.0383209822992</v>
+        <v>252.6444989610592</v>
       </c>
       <c r="D28">
-        <v>335.5583209822992</v>
+        <v>336.5344989610592</v>
       </c>
       <c r="E28">
-        <v>-38.17999999999999</v>
+        <v>-34.80999999999999</v>
       </c>
       <c r="F28">
-        <v>87.62</v>
+        <v>90.99000000000001</v>
       </c>
       <c r="G28">
         <v>7.1</v>
@@ -3583,28 +3583,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M28">
-        <v>4.845386</v>
+        <v>5.031747000000001</v>
       </c>
       <c r="N28">
-        <v>18.11016955555555</v>
+        <v>17.92380855555555</v>
       </c>
       <c r="O28">
-        <v>3.622033911111111</v>
+        <v>3.584761711111111</v>
       </c>
       <c r="P28">
-        <v>14.48813564444444</v>
+        <v>14.33904684444444</v>
       </c>
       <c r="Q28">
-        <v>23.08813564444444</v>
+        <v>22.93904684444444</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07446213621228512</v>
+        <v>0.0747934712358362</v>
       </c>
       <c r="T28">
-        <v>0.5437101326324653</v>
+        <v>0.5499954355933632</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.737611318387339</v>
+        <v>4.56214423252114</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06654403400216043</v>
+        <v>0.06704368720722985</v>
       </c>
       <c r="C29">
-        <v>252.6444989610592</v>
+        <v>241.359180900591</v>
       </c>
       <c r="D29">
-        <v>336.5344989610592</v>
+        <v>328.6191809005909</v>
       </c>
       <c r="E29">
-        <v>-34.80999999999999</v>
+        <v>-31.43999999999998</v>
       </c>
       <c r="F29">
-        <v>90.99000000000001</v>
+        <v>94.36000000000001</v>
       </c>
       <c r="G29">
         <v>7.1</v>
@@ -3665,45 +3665,45 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M29">
-        <v>5.031747000000001</v>
+        <v>5.454008000000001</v>
       </c>
       <c r="N29">
-        <v>17.92380855555555</v>
+        <v>17.50154755555555</v>
       </c>
       <c r="O29">
-        <v>3.584761711111111</v>
+        <v>3.500309511111111</v>
       </c>
       <c r="P29">
-        <v>14.33904684444444</v>
+        <v>14.00123804444444</v>
       </c>
       <c r="Q29">
-        <v>22.93904684444444</v>
+        <v>22.60123804444444</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0747934712358362</v>
+        <v>0.07513401001004145</v>
       </c>
       <c r="T29">
-        <v>0.5499954355933632</v>
+        <v>0.5564553303031747</v>
       </c>
       <c r="U29">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.56214423252114</v>
+        <v>4.208933238740308</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06704368720722985</v>
+        <v>0.06700334041229927</v>
       </c>
       <c r="C30">
-        <v>241.359180900591</v>
+        <v>238.614494197658</v>
       </c>
       <c r="D30">
-        <v>328.6191809005909</v>
+        <v>329.244494197658</v>
       </c>
       <c r="E30">
-        <v>-31.43999999999998</v>
+        <v>-28.06999999999998</v>
       </c>
       <c r="F30">
-        <v>94.36000000000001</v>
+        <v>97.73000000000002</v>
       </c>
       <c r="G30">
         <v>7.1</v>
@@ -3747,28 +3747,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M30">
-        <v>5.454008000000001</v>
+        <v>5.648794000000001</v>
       </c>
       <c r="N30">
-        <v>17.50154755555555</v>
+        <v>17.30676155555555</v>
       </c>
       <c r="O30">
-        <v>3.500309511111111</v>
+        <v>3.461352311111111</v>
       </c>
       <c r="P30">
-        <v>14.00123804444444</v>
+        <v>13.84540924444444</v>
       </c>
       <c r="Q30">
-        <v>22.60123804444444</v>
+        <v>22.44540924444444</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07513401001004145</v>
+        <v>0.07548414142577363</v>
       </c>
       <c r="T30">
-        <v>0.5564553303031747</v>
+        <v>0.5630971938780515</v>
       </c>
       <c r="U30">
         <v>0.0578</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.208933238740308</v>
+        <v>4.063797609818229</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06700334041229927</v>
+        <v>0.0678029936173687</v>
       </c>
       <c r="C31">
-        <v>238.614494197658</v>
+        <v>223.2787853666201</v>
       </c>
       <c r="D31">
-        <v>329.244494197658</v>
+        <v>317.2787853666201</v>
       </c>
       <c r="E31">
-        <v>-28.07000000000001</v>
+        <v>-24.7</v>
       </c>
       <c r="F31">
-        <v>97.72999999999999</v>
+        <v>101.1</v>
       </c>
       <c r="G31">
         <v>7.1</v>
@@ -3829,45 +3829,45 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M31">
-        <v>5.648794</v>
+        <v>6.19743</v>
       </c>
       <c r="N31">
-        <v>17.30676155555556</v>
+        <v>16.75812555555556</v>
       </c>
       <c r="O31">
-        <v>3.461352311111112</v>
+        <v>3.351625111111111</v>
       </c>
       <c r="P31">
-        <v>13.84540924444445</v>
+        <v>13.40650044444444</v>
       </c>
       <c r="Q31">
-        <v>22.44540924444444</v>
+        <v>22.00650044444444</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07548414142577363</v>
+        <v>0.07584427659624102</v>
       </c>
       <c r="T31">
-        <v>0.5630971938780515</v>
+        <v>0.5699288249836391</v>
       </c>
       <c r="U31">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.06379760981823</v>
+        <v>3.704044346697834</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0678029936173687</v>
+        <v>0.06779064682243813</v>
       </c>
       <c r="C32">
-        <v>223.2787853666201</v>
+        <v>220.0869236510632</v>
       </c>
       <c r="D32">
-        <v>317.2787853666201</v>
+        <v>317.4569236510632</v>
       </c>
       <c r="E32">
-        <v>-24.7</v>
+        <v>-21.33</v>
       </c>
       <c r="F32">
-        <v>101.1</v>
+        <v>104.47</v>
       </c>
       <c r="G32">
         <v>7.1</v>
@@ -3911,28 +3911,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M32">
-        <v>6.19743</v>
+        <v>6.404011</v>
       </c>
       <c r="N32">
-        <v>16.75812555555556</v>
+        <v>16.55154455555556</v>
       </c>
       <c r="O32">
-        <v>3.351625111111111</v>
+        <v>3.310308911111111</v>
       </c>
       <c r="P32">
-        <v>13.40650044444444</v>
+        <v>13.24123564444444</v>
       </c>
       <c r="Q32">
-        <v>22.00650044444444</v>
+        <v>21.84123564444444</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07584427659624102</v>
+        <v>0.07621485046730164</v>
       </c>
       <c r="T32">
-        <v>0.5699288249836391</v>
+        <v>0.5769584743821421</v>
       </c>
       <c r="U32">
         <v>0.0613</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.704044346697834</v>
+        <v>3.584559045191452</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06779064682243813</v>
+        <v>0.06849510002750755</v>
       </c>
       <c r="C33">
-        <v>220.0869236510632</v>
+        <v>206.8630985052644</v>
       </c>
       <c r="D33">
-        <v>317.4569236510632</v>
+        <v>307.6030985052644</v>
       </c>
       <c r="E33">
-        <v>-21.33</v>
+        <v>-17.95999999999999</v>
       </c>
       <c r="F33">
-        <v>104.47</v>
+        <v>107.84</v>
       </c>
       <c r="G33">
         <v>7.1</v>
@@ -3993,45 +3993,45 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M33">
-        <v>6.404011</v>
+        <v>6.912544</v>
       </c>
       <c r="N33">
-        <v>16.55154455555556</v>
+        <v>16.04301155555556</v>
       </c>
       <c r="O33">
-        <v>3.310308911111111</v>
+        <v>3.208602311111111</v>
       </c>
       <c r="P33">
-        <v>13.24123564444444</v>
+        <v>12.83440924444444</v>
       </c>
       <c r="Q33">
-        <v>21.84123564444444</v>
+        <v>21.43440924444444</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07621485046730164</v>
+        <v>0.07659632356986407</v>
       </c>
       <c r="T33">
-        <v>0.5769584743821421</v>
+        <v>0.5841948781747188</v>
       </c>
       <c r="U33">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.584559045191452</v>
+        <v>3.320854891564604</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06849510002750755</v>
+        <v>0.06850515323257698</v>
       </c>
       <c r="C34">
-        <v>206.8630985052644</v>
+        <v>203.3569004801911</v>
       </c>
       <c r="D34">
-        <v>307.6030985052644</v>
+        <v>307.466900480191</v>
       </c>
       <c r="E34">
-        <v>-17.95999999999999</v>
+        <v>-14.58999999999999</v>
       </c>
       <c r="F34">
-        <v>107.84</v>
+        <v>111.21</v>
       </c>
       <c r="G34">
         <v>7.1</v>
@@ -4075,28 +4075,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M34">
-        <v>6.912544</v>
+        <v>7.128561000000001</v>
       </c>
       <c r="N34">
-        <v>16.04301155555556</v>
+        <v>15.82699455555555</v>
       </c>
       <c r="O34">
-        <v>3.208602311111111</v>
+        <v>3.165398911111111</v>
       </c>
       <c r="P34">
-        <v>12.83440924444444</v>
+        <v>12.66159564444444</v>
       </c>
       <c r="Q34">
-        <v>21.43440924444444</v>
+        <v>21.26159564444444</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07659632356986407</v>
+        <v>0.07698918392921938</v>
       </c>
       <c r="T34">
-        <v>0.5841948781747188</v>
+        <v>0.5916472940208053</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.320854891564604</v>
+        <v>3.220222925153555</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06850515323257698</v>
+        <v>0.06851520643764641</v>
       </c>
       <c r="C35">
-        <v>203.3569004801911</v>
+        <v>199.8508230110703</v>
       </c>
       <c r="D35">
-        <v>307.466900480191</v>
+        <v>307.3308230110703</v>
       </c>
       <c r="E35">
-        <v>-14.58999999999999</v>
+        <v>-11.21999999999998</v>
       </c>
       <c r="F35">
-        <v>111.21</v>
+        <v>114.58</v>
       </c>
       <c r="G35">
         <v>7.1</v>
@@ -4157,28 +4157,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M35">
-        <v>7.128561000000001</v>
+        <v>7.344578000000001</v>
       </c>
       <c r="N35">
-        <v>15.82699455555555</v>
+        <v>15.61097755555555</v>
       </c>
       <c r="O35">
-        <v>3.165398911111111</v>
+        <v>3.122195511111111</v>
       </c>
       <c r="P35">
-        <v>12.66159564444444</v>
+        <v>12.48878204444444</v>
       </c>
       <c r="Q35">
-        <v>21.26159564444444</v>
+        <v>21.08878204444444</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07698918392921938</v>
+        <v>0.07739394914794911</v>
       </c>
       <c r="T35">
-        <v>0.5916472940208053</v>
+        <v>0.5993255406501065</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.220222925153555</v>
+        <v>3.125510486178451</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06851520643764641</v>
+        <v>0.06852525964271584</v>
       </c>
       <c r="C36">
-        <v>199.8508230110703</v>
+        <v>196.3448659379076</v>
       </c>
       <c r="D36">
-        <v>307.3308230110703</v>
+        <v>307.1948659379076</v>
       </c>
       <c r="E36">
-        <v>-11.21999999999998</v>
+        <v>-7.84999999999998</v>
       </c>
       <c r="F36">
-        <v>114.58</v>
+        <v>117.95</v>
       </c>
       <c r="G36">
         <v>7.1</v>
@@ -4239,28 +4239,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M36">
-        <v>7.344578000000001</v>
+        <v>7.560595000000002</v>
       </c>
       <c r="N36">
-        <v>15.61097755555555</v>
+        <v>15.39496055555555</v>
       </c>
       <c r="O36">
-        <v>3.122195511111111</v>
+        <v>3.078992111111111</v>
       </c>
       <c r="P36">
-        <v>12.48878204444444</v>
+        <v>12.31596844444444</v>
       </c>
       <c r="Q36">
-        <v>21.08878204444444</v>
+        <v>20.91596844444444</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07739394914794911</v>
+        <v>0.0778111686811013</v>
       </c>
       <c r="T36">
-        <v>0.5993255406501065</v>
+        <v>0.6072400410218478</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.125510486178451</v>
+        <v>3.036210186573352</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06852525964271584</v>
+        <v>0.07078171284778527</v>
       </c>
       <c r="C37">
-        <v>196.3448659379076</v>
+        <v>165.2277357050855</v>
       </c>
       <c r="D37">
-        <v>307.1948659379076</v>
+        <v>279.4477357050854</v>
       </c>
       <c r="E37">
-        <v>-7.84999999999998</v>
+        <v>-4.47999999999999</v>
       </c>
       <c r="F37">
-        <v>117.95</v>
+        <v>121.32</v>
       </c>
       <c r="G37">
         <v>7.1</v>
@@ -4321,45 +4321,45 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M37">
-        <v>7.560595000000002</v>
+        <v>8.722908</v>
       </c>
       <c r="N37">
-        <v>15.39496055555555</v>
+        <v>14.23264755555556</v>
       </c>
       <c r="O37">
-        <v>3.078992111111111</v>
+        <v>2.846529511111111</v>
       </c>
       <c r="P37">
-        <v>12.31596844444444</v>
+        <v>11.38611804444444</v>
       </c>
       <c r="Q37">
-        <v>20.91596844444444</v>
+        <v>19.98611804444444</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0778111686811013</v>
+        <v>0.07824142632466449</v>
       </c>
       <c r="T37">
-        <v>0.6072400410218478</v>
+        <v>0.615401869530206</v>
       </c>
       <c r="U37">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V37">
         <v>0.2</v>
       </c>
       <c r="W37">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.036210186573352</v>
+        <v>2.631640223140672</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07078171284778528</v>
+        <v>0.0708541660528547</v>
       </c>
       <c r="C38">
-        <v>165.2277357050853</v>
+        <v>161.0496112574979</v>
       </c>
       <c r="D38">
-        <v>279.4477357050853</v>
+        <v>278.6396112574979</v>
       </c>
       <c r="E38">
-        <v>-4.480000000000004</v>
+        <v>-1.109999999999999</v>
       </c>
       <c r="F38">
-        <v>121.32</v>
+        <v>124.69</v>
       </c>
       <c r="G38">
         <v>7.1</v>
@@ -4403,28 +4403,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M38">
-        <v>8.722908</v>
+        <v>8.965211</v>
       </c>
       <c r="N38">
-        <v>14.23264755555556</v>
+        <v>13.99034455555556</v>
       </c>
       <c r="O38">
-        <v>2.846529511111111</v>
+        <v>2.798068911111111</v>
       </c>
       <c r="P38">
-        <v>11.38611804444444</v>
+        <v>11.19227564444444</v>
       </c>
       <c r="Q38">
-        <v>19.98611804444444</v>
+        <v>19.79227564444444</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07824142632466449</v>
+        <v>0.07868534294103921</v>
       </c>
       <c r="T38">
-        <v>0.6154018695302059</v>
+        <v>0.6238228037054961</v>
       </c>
       <c r="U38">
         <v>0.07190000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.631640223140672</v>
+        <v>2.560514811704438</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0708541660528547</v>
+        <v>0.07211221925792413</v>
       </c>
       <c r="C39">
-        <v>161.0496112574979</v>
+        <v>144.3571524954448</v>
       </c>
       <c r="D39">
-        <v>278.6396112574979</v>
+        <v>265.3171524954448</v>
       </c>
       <c r="E39">
-        <v>-1.109999999999999</v>
+        <v>2.260000000000005</v>
       </c>
       <c r="F39">
-        <v>124.69</v>
+        <v>128.06</v>
       </c>
       <c r="G39">
         <v>7.1</v>
@@ -4485,45 +4485,45 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M39">
-        <v>8.965211</v>
+        <v>9.706948000000001</v>
       </c>
       <c r="N39">
-        <v>13.99034455555556</v>
+        <v>13.24860755555556</v>
       </c>
       <c r="O39">
-        <v>2.798068911111111</v>
+        <v>2.649721511111111</v>
       </c>
       <c r="P39">
-        <v>11.19227564444444</v>
+        <v>10.59888604444444</v>
       </c>
       <c r="Q39">
-        <v>19.79227564444444</v>
+        <v>19.19888604444444</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.07868534294103921</v>
+        <v>0.07914357944826472</v>
       </c>
       <c r="T39">
-        <v>0.6238228037054961</v>
+        <v>0.6325153809186989</v>
       </c>
       <c r="U39">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V39">
         <v>0.2</v>
       </c>
       <c r="W39">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.560514811704438</v>
+        <v>2.364858198020176</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07211221925792413</v>
+        <v>0.07221587246299356</v>
       </c>
       <c r="C40">
-        <v>144.3571524954448</v>
+        <v>139.9460748912667</v>
       </c>
       <c r="D40">
-        <v>265.3171524954448</v>
+        <v>264.2760748912667</v>
       </c>
       <c r="E40">
-        <v>2.260000000000005</v>
+        <v>5.63000000000001</v>
       </c>
       <c r="F40">
-        <v>128.06</v>
+        <v>131.43</v>
       </c>
       <c r="G40">
         <v>7.1</v>
@@ -4567,28 +4567,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M40">
-        <v>9.706948000000001</v>
+        <v>9.962394000000002</v>
       </c>
       <c r="N40">
-        <v>13.24860755555556</v>
+        <v>12.99316155555555</v>
       </c>
       <c r="O40">
-        <v>2.649721511111111</v>
+        <v>2.598632311111111</v>
       </c>
       <c r="P40">
-        <v>10.59888604444444</v>
+        <v>10.39452924444444</v>
       </c>
       <c r="Q40">
-        <v>19.19888604444444</v>
+        <v>18.99452924444444</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.07914357944826472</v>
+        <v>0.07961684010326814</v>
       </c>
       <c r="T40">
-        <v>0.6325153809186989</v>
+        <v>0.641492960663482</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.364858198020176</v>
+        <v>2.304220808327351</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07221587246299356</v>
+        <v>0.07231952566806299</v>
       </c>
       <c r="C41">
-        <v>139.9460748912667</v>
+        <v>135.5431355194046</v>
       </c>
       <c r="D41">
-        <v>264.2760748912667</v>
+        <v>263.2431355194046</v>
       </c>
       <c r="E41">
-        <v>5.63000000000001</v>
+        <v>9.000000000000014</v>
       </c>
       <c r="F41">
-        <v>131.43</v>
+        <v>134.8</v>
       </c>
       <c r="G41">
         <v>7.1</v>
@@ -4649,28 +4649,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M41">
-        <v>9.962394000000002</v>
+        <v>10.21784</v>
       </c>
       <c r="N41">
-        <v>12.99316155555555</v>
+        <v>12.73771555555555</v>
       </c>
       <c r="O41">
-        <v>2.598632311111111</v>
+        <v>2.547543111111111</v>
       </c>
       <c r="P41">
-        <v>10.39452924444444</v>
+        <v>10.19017244444444</v>
       </c>
       <c r="Q41">
-        <v>18.99452924444444</v>
+        <v>18.79017244444444</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.07961684010326814</v>
+        <v>0.08010587611343831</v>
       </c>
       <c r="T41">
-        <v>0.641492960663482</v>
+        <v>0.6507697930664247</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.304220808327351</v>
+        <v>2.246615288119167</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07231952566806299</v>
+        <v>0.07242317887313242</v>
       </c>
       <c r="C42">
-        <v>135.5431355194046</v>
+        <v>131.1482393250344</v>
       </c>
       <c r="D42">
-        <v>263.2431355194046</v>
+        <v>262.2182393250344</v>
       </c>
       <c r="E42">
-        <v>9.000000000000014</v>
+        <v>12.37000000000002</v>
       </c>
       <c r="F42">
-        <v>134.8</v>
+        <v>138.17</v>
       </c>
       <c r="G42">
         <v>7.1</v>
@@ -4731,28 +4731,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M42">
-        <v>10.21784</v>
+        <v>10.473286</v>
       </c>
       <c r="N42">
-        <v>12.73771555555555</v>
+        <v>12.48226955555555</v>
       </c>
       <c r="O42">
-        <v>2.547543111111111</v>
+        <v>2.496453911111111</v>
       </c>
       <c r="P42">
-        <v>10.19017244444444</v>
+        <v>9.985815644444443</v>
       </c>
       <c r="Q42">
-        <v>18.79017244444444</v>
+        <v>18.58581564444444</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08010587611343831</v>
+        <v>0.08061148961547868</v>
       </c>
       <c r="T42">
-        <v>0.6507697930664247</v>
+        <v>0.6603610943643823</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.246615288119167</v>
+        <v>2.191819793286992</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07242317887313242</v>
+        <v>0.07252683207820185</v>
       </c>
       <c r="C43">
-        <v>131.1482393250344</v>
+        <v>126.7612927279152</v>
       </c>
       <c r="D43">
-        <v>262.2182393250344</v>
+        <v>261.2012927279152</v>
       </c>
       <c r="E43">
-        <v>12.37000000000002</v>
+        <v>15.74000000000002</v>
       </c>
       <c r="F43">
-        <v>138.17</v>
+        <v>141.54</v>
       </c>
       <c r="G43">
         <v>7.1</v>
@@ -4813,28 +4813,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M43">
-        <v>10.473286</v>
+        <v>10.728732</v>
       </c>
       <c r="N43">
-        <v>12.48226955555555</v>
+        <v>12.22682355555555</v>
       </c>
       <c r="O43">
-        <v>2.496453911111111</v>
+        <v>2.445364711111111</v>
       </c>
       <c r="P43">
-        <v>9.985815644444443</v>
+        <v>9.781458844444442</v>
       </c>
       <c r="Q43">
-        <v>18.58581564444444</v>
+        <v>18.38145884444444</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08061148961547868</v>
+        <v>0.08113453806586526</v>
       </c>
       <c r="T43">
-        <v>0.6603610943643823</v>
+        <v>0.6702831301898557</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.191819793286992</v>
+        <v>2.13963360773254</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07252683207820185</v>
+        <v>0.07263048528327129</v>
       </c>
       <c r="C44">
-        <v>126.7612927279152</v>
+        <v>122.3822035939066</v>
       </c>
       <c r="D44">
-        <v>261.2012927279152</v>
+        <v>260.1922035939065</v>
       </c>
       <c r="E44">
-        <v>15.73999999999999</v>
+        <v>19.11</v>
       </c>
       <c r="F44">
-        <v>141.54</v>
+        <v>144.91</v>
       </c>
       <c r="G44">
         <v>7.1</v>
@@ -4895,28 +4895,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M44">
-        <v>10.728732</v>
+        <v>10.984178</v>
       </c>
       <c r="N44">
-        <v>12.22682355555555</v>
+        <v>11.97137755555556</v>
       </c>
       <c r="O44">
-        <v>2.445364711111111</v>
+        <v>2.394275511111111</v>
       </c>
       <c r="P44">
-        <v>9.781458844444444</v>
+        <v>9.577102044444445</v>
       </c>
       <c r="Q44">
-        <v>18.38145884444444</v>
+        <v>18.17710204444444</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08113453806586525</v>
+        <v>0.08167593909345838</v>
       </c>
       <c r="T44">
-        <v>0.6702831301898556</v>
+        <v>0.6805533076232405</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.139633607732541</v>
+        <v>2.089874686622482</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07263048528327129</v>
+        <v>0.0727341384883407</v>
       </c>
       <c r="C45">
-        <v>122.3822035939066</v>
+        <v>118.0108812071424</v>
       </c>
       <c r="D45">
-        <v>260.1922035939065</v>
+        <v>259.1908812071424</v>
       </c>
       <c r="E45">
-        <v>19.11</v>
+        <v>22.48</v>
       </c>
       <c r="F45">
-        <v>144.91</v>
+        <v>148.28</v>
       </c>
       <c r="G45">
         <v>7.1</v>
@@ -4977,28 +4977,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M45">
-        <v>10.984178</v>
+        <v>11.239624</v>
       </c>
       <c r="N45">
-        <v>11.97137755555556</v>
+        <v>11.71593155555555</v>
       </c>
       <c r="O45">
-        <v>2.394275511111111</v>
+        <v>2.343186311111111</v>
       </c>
       <c r="P45">
-        <v>9.577102044444445</v>
+        <v>9.372745244444443</v>
       </c>
       <c r="Q45">
-        <v>18.17710204444444</v>
+        <v>17.97274524444444</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08167593909345838</v>
+        <v>0.08223667587203697</v>
       </c>
       <c r="T45">
-        <v>0.6805533076232405</v>
+        <v>0.6911902771078174</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.089874686622482</v>
+        <v>2.042377534653789</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0727341384883407</v>
+        <v>0.07794979169341013</v>
       </c>
       <c r="C46">
-        <v>118.0108812071424</v>
+        <v>72.59240502463896</v>
       </c>
       <c r="D46">
-        <v>259.1908812071424</v>
+        <v>217.142405024639</v>
       </c>
       <c r="E46">
-        <v>22.48</v>
+        <v>25.85000000000001</v>
       </c>
       <c r="F46">
-        <v>148.28</v>
+        <v>151.65</v>
       </c>
       <c r="G46">
         <v>7.1</v>
@@ -5059,45 +5059,45 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M46">
-        <v>11.239624</v>
+        <v>13.6485</v>
       </c>
       <c r="N46">
-        <v>11.71593155555555</v>
+        <v>9.307055555555555</v>
       </c>
       <c r="O46">
-        <v>2.343186311111111</v>
+        <v>1.861411111111111</v>
       </c>
       <c r="P46">
-        <v>9.372745244444443</v>
+        <v>7.445644444444445</v>
       </c>
       <c r="Q46">
-        <v>17.97274524444444</v>
+        <v>16.04564444444444</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08223667587203697</v>
+        <v>0.0828178030789275</v>
       </c>
       <c r="T46">
-        <v>0.6911902771078174</v>
+        <v>0.7022140454827428</v>
       </c>
       <c r="U46">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V46">
         <v>0.2</v>
       </c>
       <c r="W46">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.042377534653789</v>
+        <v>1.681910507056128</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07794979169341013</v>
+        <v>0.07816704489847956</v>
       </c>
       <c r="C47">
-        <v>72.59240502463896</v>
+        <v>67.76490763505475</v>
       </c>
       <c r="D47">
-        <v>217.142405024639</v>
+        <v>215.6849076350548</v>
       </c>
       <c r="E47">
-        <v>25.85000000000001</v>
+        <v>29.22000000000001</v>
       </c>
       <c r="F47">
-        <v>151.65</v>
+        <v>155.02</v>
       </c>
       <c r="G47">
         <v>7.1</v>
@@ -5141,28 +5141,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M47">
-        <v>13.6485</v>
+        <v>13.9518</v>
       </c>
       <c r="N47">
-        <v>9.307055555555555</v>
+        <v>9.003755555555555</v>
       </c>
       <c r="O47">
-        <v>1.861411111111111</v>
+        <v>1.800751111111111</v>
       </c>
       <c r="P47">
-        <v>7.445644444444445</v>
+        <v>7.203004444444444</v>
       </c>
       <c r="Q47">
-        <v>16.04564444444444</v>
+        <v>15.80300444444444</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.0828178030789275</v>
+        <v>0.08342045351570289</v>
       </c>
       <c r="T47">
-        <v>0.7022140454827428</v>
+        <v>0.713646101575258</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.681910507056128</v>
+        <v>1.645347235163603</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07816704489847956</v>
+        <v>0.07838429810354899</v>
       </c>
       <c r="C48">
-        <v>67.76490763505475</v>
+        <v>62.95684574033754</v>
       </c>
       <c r="D48">
-        <v>215.6849076350548</v>
+        <v>214.2468457403376</v>
       </c>
       <c r="E48">
-        <v>29.22000000000001</v>
+        <v>32.59000000000002</v>
       </c>
       <c r="F48">
-        <v>155.02</v>
+        <v>158.39</v>
       </c>
       <c r="G48">
         <v>7.1</v>
@@ -5223,28 +5223,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M48">
-        <v>13.9518</v>
+        <v>14.2551</v>
       </c>
       <c r="N48">
-        <v>9.003755555555555</v>
+        <v>8.700455555555555</v>
       </c>
       <c r="O48">
-        <v>1.800751111111111</v>
+        <v>1.740091111111111</v>
       </c>
       <c r="P48">
-        <v>7.203004444444444</v>
+        <v>6.960364444444444</v>
       </c>
       <c r="Q48">
-        <v>15.80300444444444</v>
+        <v>15.56036444444444</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08342045351570289</v>
+        <v>0.08404584547839432</v>
       </c>
       <c r="T48">
-        <v>0.713646101575258</v>
+        <v>0.725509556010887</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.645347235163603</v>
+        <v>1.610339847181399</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07838429810354899</v>
+        <v>0.07860155130861841</v>
       </c>
       <c r="C49">
-        <v>62.95684574033754</v>
+        <v>58.16783316147598</v>
       </c>
       <c r="D49">
-        <v>214.2468457403376</v>
+        <v>212.827833161476</v>
       </c>
       <c r="E49">
-        <v>32.59000000000002</v>
+        <v>35.96000000000002</v>
       </c>
       <c r="F49">
-        <v>158.39</v>
+        <v>161.76</v>
       </c>
       <c r="G49">
         <v>7.1</v>
@@ -5305,28 +5305,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M49">
-        <v>14.2551</v>
+        <v>14.5584</v>
       </c>
       <c r="N49">
-        <v>8.700455555555555</v>
+        <v>8.397155555555555</v>
       </c>
       <c r="O49">
-        <v>1.740091111111111</v>
+        <v>1.679431111111111</v>
       </c>
       <c r="P49">
-        <v>6.960364444444444</v>
+        <v>6.717724444444444</v>
       </c>
       <c r="Q49">
-        <v>15.56036444444444</v>
+        <v>15.31772444444444</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08404584547839432</v>
+        <v>0.08469529097811233</v>
       </c>
       <c r="T49">
-        <v>0.725509556010887</v>
+        <v>0.7378292971555784</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.610339847181399</v>
+        <v>1.576791100365119</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0786015513086184</v>
+        <v>0.07881880451368783</v>
       </c>
       <c r="C50">
-        <v>58.16783316147612</v>
+        <v>53.39749388319771</v>
       </c>
       <c r="D50">
-        <v>212.8278331614761</v>
+        <v>211.4274938831977</v>
       </c>
       <c r="E50">
-        <v>35.95999999999999</v>
+        <v>39.33</v>
       </c>
       <c r="F50">
-        <v>161.76</v>
+        <v>165.13</v>
       </c>
       <c r="G50">
         <v>7.1</v>
@@ -5387,28 +5387,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M50">
-        <v>14.5584</v>
+        <v>14.8617</v>
       </c>
       <c r="N50">
-        <v>8.397155555555557</v>
+        <v>8.093855555555557</v>
       </c>
       <c r="O50">
-        <v>1.679431111111112</v>
+        <v>1.618771111111111</v>
       </c>
       <c r="P50">
-        <v>6.717724444444445</v>
+        <v>6.475084444444446</v>
       </c>
       <c r="Q50">
-        <v>15.31772444444444</v>
+        <v>15.07508444444444</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08469529097811233</v>
+        <v>0.08537020492879968</v>
       </c>
       <c r="T50">
-        <v>0.7378292971555784</v>
+        <v>0.7506321654039834</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.57679110036512</v>
+        <v>1.544611690153586</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07881880451368783</v>
+        <v>0.07903605771875727</v>
       </c>
       <c r="C51">
-        <v>53.39749388319771</v>
+        <v>48.64546172178407</v>
       </c>
       <c r="D51">
-        <v>211.4274938831977</v>
+        <v>210.0454617217841</v>
       </c>
       <c r="E51">
-        <v>39.33</v>
+        <v>42.7</v>
       </c>
       <c r="F51">
-        <v>165.13</v>
+        <v>168.5</v>
       </c>
       <c r="G51">
         <v>7.1</v>
@@ -5469,28 +5469,28 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M51">
-        <v>14.8617</v>
+        <v>15.165</v>
       </c>
       <c r="N51">
-        <v>8.093855555555557</v>
+        <v>7.790555555555557</v>
       </c>
       <c r="O51">
-        <v>1.618771111111111</v>
+        <v>1.558111111111111</v>
       </c>
       <c r="P51">
-        <v>6.475084444444446</v>
+        <v>6.232444444444445</v>
       </c>
       <c r="Q51">
-        <v>15.07508444444444</v>
+        <v>14.83244444444444</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08537020492879968</v>
+        <v>0.08607211543751454</v>
       </c>
       <c r="T51">
-        <v>0.7506321654039834</v>
+        <v>0.7639471483823246</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.544611690153586</v>
+        <v>1.513719456350515</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07903605771875727</v>
+        <v>0.1039836047598288</v>
       </c>
       <c r="C52">
-        <v>48.64546172178407</v>
+        <v>-44.78631871787833</v>
       </c>
       <c r="D52">
-        <v>210.0454617217841</v>
+        <v>119.9836812821217</v>
       </c>
       <c r="E52">
-        <v>42.7</v>
+        <v>46.07000000000001</v>
       </c>
       <c r="F52">
-        <v>168.5</v>
+        <v>171.87</v>
       </c>
       <c r="G52">
         <v>7.1</v>
@@ -5551,45 +5551,45 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M52">
-        <v>15.165</v>
+        <v>25.230516</v>
       </c>
       <c r="N52">
-        <v>7.790555555555557</v>
+        <v>-2.274960444444446</v>
       </c>
       <c r="O52">
-        <v>1.558111111111111</v>
+        <v>-0.4549920888888892</v>
       </c>
       <c r="P52">
-        <v>6.232444444444445</v>
+        <v>-1.819968355555557</v>
       </c>
       <c r="Q52">
-        <v>14.83244444444444</v>
+        <v>6.780031644444441</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08607211543751454</v>
+        <v>0.08722261197343555</v>
       </c>
       <c r="T52">
-        <v>0.7639471483823246</v>
+        <v>0.7857716425339741</v>
       </c>
       <c r="U52">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2</v>
+        <v>0.1819665959709707</v>
       </c>
       <c r="W52">
-        <v>0.07199999999999999</v>
+        <v>0.1200873037114615</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y52">
-        <v>1.513719456350515</v>
+        <v>0.9098329798548533</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1039836047598288</v>
+        <v>0.1049936047598288</v>
       </c>
       <c r="C53">
-        <v>-44.78631871787833</v>
+        <v>-50.20355876326214</v>
       </c>
       <c r="D53">
-        <v>119.9836812821217</v>
+        <v>117.9364412367379</v>
       </c>
       <c r="E53">
-        <v>46.07000000000001</v>
+        <v>49.44000000000001</v>
       </c>
       <c r="F53">
-        <v>171.87</v>
+        <v>175.24</v>
       </c>
       <c r="G53">
         <v>7.1</v>
@@ -5633,37 +5633,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M53">
-        <v>25.230516</v>
+        <v>25.72523200000001</v>
       </c>
       <c r="N53">
-        <v>-2.274960444444446</v>
+        <v>-2.76967644444445</v>
       </c>
       <c r="O53">
-        <v>-0.4549920888888892</v>
+        <v>-0.55393528888889</v>
       </c>
       <c r="P53">
-        <v>-1.819968355555557</v>
+        <v>-2.21574115555556</v>
       </c>
       <c r="Q53">
-        <v>6.780031644444441</v>
+        <v>6.384258844444438</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08722261197343555</v>
+        <v>0.08808558305621544</v>
       </c>
       <c r="T53">
-        <v>0.7857716425339741</v>
+        <v>0.8021418850867652</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.1819665959709707</v>
+        <v>0.1784672383561443</v>
       </c>
       <c r="W53">
-        <v>0.1200873037114615</v>
+        <v>0.120601009409318</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.9098329798548533</v>
+        <v>0.8923361917807214</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1049936047598288</v>
+        <v>0.1060036047598288</v>
       </c>
       <c r="C54">
-        <v>-50.20355876326214</v>
+        <v>-55.55210815618132</v>
       </c>
       <c r="D54">
-        <v>117.9364412367379</v>
+        <v>115.9578918438187</v>
       </c>
       <c r="E54">
-        <v>49.44000000000001</v>
+        <v>52.81000000000002</v>
       </c>
       <c r="F54">
-        <v>175.24</v>
+        <v>178.61</v>
       </c>
       <c r="G54">
         <v>7.1</v>
@@ -5715,37 +5715,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M54">
-        <v>25.72523200000001</v>
+        <v>26.21994800000001</v>
       </c>
       <c r="N54">
-        <v>-2.76967644444445</v>
+        <v>-3.26439244444445</v>
       </c>
       <c r="O54">
-        <v>-0.55393528888889</v>
+        <v>-0.6528784888888901</v>
       </c>
       <c r="P54">
-        <v>-2.21574115555556</v>
+        <v>-2.61151395555556</v>
       </c>
       <c r="Q54">
-        <v>6.384258844444438</v>
+        <v>5.988486044444437</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.08808558305621544</v>
+        <v>0.08898527631273068</v>
       </c>
       <c r="T54">
-        <v>0.8021418850867652</v>
+        <v>0.8192087337056327</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.1784672383561443</v>
+        <v>0.1750999319720661</v>
       </c>
       <c r="W54">
-        <v>0.120601009409318</v>
+        <v>0.1210953299865007</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8923361917807214</v>
+        <v>0.8754996598603304</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1060036047598288</v>
+        <v>0.1070136047598288</v>
       </c>
       <c r="C55">
-        <v>-55.55210815618132</v>
+        <v>-60.83536700152733</v>
       </c>
       <c r="D55">
-        <v>115.9578918438187</v>
+        <v>114.0446329984727</v>
       </c>
       <c r="E55">
-        <v>52.81000000000002</v>
+        <v>56.18000000000002</v>
       </c>
       <c r="F55">
-        <v>178.61</v>
+        <v>181.98</v>
       </c>
       <c r="G55">
         <v>7.1</v>
@@ -5797,37 +5797,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M55">
-        <v>26.21994800000001</v>
+        <v>26.71466400000001</v>
       </c>
       <c r="N55">
-        <v>-3.26439244444445</v>
+        <v>-3.75910844444445</v>
       </c>
       <c r="O55">
-        <v>-0.6528784888888901</v>
+        <v>-0.7518216888888901</v>
       </c>
       <c r="P55">
-        <v>-2.61151395555556</v>
+        <v>-3.00728675555556</v>
       </c>
       <c r="Q55">
-        <v>5.988486044444437</v>
+        <v>5.592713244444438</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.08898527631273068</v>
+        <v>0.08992408666735525</v>
       </c>
       <c r="T55">
-        <v>0.8192087337056327</v>
+        <v>0.8370176192209725</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1750999319720661</v>
+        <v>0.1718573406392501</v>
       </c>
       <c r="W55">
-        <v>0.1210953299865007</v>
+        <v>0.1215713423941581</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8754996598603304</v>
+        <v>0.8592867031962502</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1070136047598288</v>
+        <v>0.1080236047598288</v>
       </c>
       <c r="C56">
-        <v>-60.83536700152733</v>
+        <v>-66.05651464514345</v>
       </c>
       <c r="D56">
-        <v>114.0446329984727</v>
+        <v>112.1934853548566</v>
       </c>
       <c r="E56">
-        <v>56.18000000000002</v>
+        <v>59.55000000000003</v>
       </c>
       <c r="F56">
-        <v>181.98</v>
+        <v>185.35</v>
       </c>
       <c r="G56">
         <v>7.1</v>
@@ -5879,37 +5879,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M56">
-        <v>26.71466400000001</v>
+        <v>27.20938000000001</v>
       </c>
       <c r="N56">
-        <v>-3.75910844444445</v>
+        <v>-4.253824444444451</v>
       </c>
       <c r="O56">
-        <v>-0.7518216888888901</v>
+        <v>-0.8507648888888902</v>
       </c>
       <c r="P56">
-        <v>-3.00728675555556</v>
+        <v>-3.403059555555561</v>
       </c>
       <c r="Q56">
-        <v>5.592713244444438</v>
+        <v>5.196940444444437</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.08992408666735525</v>
+        <v>0.09090462192662982</v>
       </c>
       <c r="T56">
-        <v>0.8370176192209725</v>
+        <v>0.8556180107592164</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1718573406392501</v>
+        <v>0.1687326617185364</v>
       </c>
       <c r="W56">
-        <v>0.1215713423941581</v>
+        <v>0.1220300452597189</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8592867031962502</v>
+        <v>0.843663308592682</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1080236047598288</v>
+        <v>0.1090336047598288</v>
       </c>
       <c r="C57">
-        <v>-66.05651464514345</v>
+        <v>-71.21852730421607</v>
       </c>
       <c r="D57">
-        <v>112.1934853548566</v>
+        <v>110.401472695784</v>
       </c>
       <c r="E57">
-        <v>59.55000000000003</v>
+        <v>62.92000000000003</v>
       </c>
       <c r="F57">
-        <v>185.35</v>
+        <v>188.72</v>
       </c>
       <c r="G57">
         <v>7.1</v>
@@ -5961,37 +5961,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M57">
-        <v>27.20938000000001</v>
+        <v>27.70409600000001</v>
       </c>
       <c r="N57">
-        <v>-4.253824444444451</v>
+        <v>-4.748540444444451</v>
       </c>
       <c r="O57">
-        <v>-0.8507648888888902</v>
+        <v>-0.9497080888888902</v>
       </c>
       <c r="P57">
-        <v>-3.403059555555561</v>
+        <v>-3.798832355555561</v>
       </c>
       <c r="Q57">
-        <v>5.196940444444437</v>
+        <v>4.801167644444437</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09090462192662982</v>
+        <v>0.09192972697041685</v>
       </c>
       <c r="T57">
-        <v>0.8556180107592164</v>
+        <v>0.8750638746401075</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1687326617185364</v>
+        <v>0.1657195784735626</v>
       </c>
       <c r="W57">
-        <v>0.1220300452597189</v>
+        <v>0.122472365880081</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.843663308592682</v>
+        <v>0.8285978923678127</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1090336047598288</v>
+        <v>0.1100436047598288</v>
       </c>
       <c r="C58">
-        <v>-71.21852730421607</v>
+        <v>-76.32419403461824</v>
       </c>
       <c r="D58">
-        <v>110.401472695784</v>
+        <v>108.6658059653818</v>
       </c>
       <c r="E58">
-        <v>62.92000000000003</v>
+        <v>66.29000000000003</v>
       </c>
       <c r="F58">
-        <v>188.72</v>
+        <v>192.09</v>
       </c>
       <c r="G58">
         <v>7.1</v>
@@ -6043,37 +6043,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M58">
-        <v>27.70409600000001</v>
+        <v>28.19881200000001</v>
       </c>
       <c r="N58">
-        <v>-4.748540444444451</v>
+        <v>-5.243256444444452</v>
       </c>
       <c r="O58">
-        <v>-0.9497080888888902</v>
+        <v>-1.04865128888889</v>
       </c>
       <c r="P58">
-        <v>-3.798832355555561</v>
+        <v>-4.194605155555561</v>
       </c>
       <c r="Q58">
-        <v>4.801167644444437</v>
+        <v>4.405394844444436</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09192972697041685</v>
+        <v>0.09300251131856609</v>
       </c>
       <c r="T58">
-        <v>0.8750638746401075</v>
+        <v>0.8954141973061566</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1657195784735626</v>
+        <v>0.1628122174477106</v>
       </c>
       <c r="W58">
-        <v>0.122472365880081</v>
+        <v>0.1228991664786761</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8285978923678127</v>
+        <v>0.8140610872385527</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1100436047598288</v>
+        <v>0.1110536047598288</v>
       </c>
       <c r="C59">
-        <v>-76.32419403461824</v>
+        <v>-81.37613121539145</v>
       </c>
       <c r="D59">
-        <v>108.6658059653818</v>
+        <v>106.9838687846086</v>
       </c>
       <c r="E59">
-        <v>66.29000000000003</v>
+        <v>69.66000000000004</v>
       </c>
       <c r="F59">
-        <v>192.09</v>
+        <v>195.46</v>
       </c>
       <c r="G59">
         <v>7.1</v>
@@ -6125,37 +6125,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M59">
-        <v>28.19881200000001</v>
+        <v>28.69352800000001</v>
       </c>
       <c r="N59">
-        <v>-5.243256444444452</v>
+        <v>-5.737972444444452</v>
       </c>
       <c r="O59">
-        <v>-1.04865128888889</v>
+        <v>-1.14759448888889</v>
       </c>
       <c r="P59">
-        <v>-4.194605155555561</v>
+        <v>-4.590377955555562</v>
       </c>
       <c r="Q59">
-        <v>4.405394844444436</v>
+        <v>4.009622044444436</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09300251131856609</v>
+        <v>0.0941263806356748</v>
       </c>
       <c r="T59">
-        <v>0.8954141973061566</v>
+        <v>0.9167335829563031</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1628122174477106</v>
+        <v>0.1600051102503363</v>
       </c>
       <c r="W59">
-        <v>0.1228991664786761</v>
+        <v>0.1233112498152506</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8140610872385527</v>
+        <v>0.8000255512516812</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1110536047598288</v>
+        <v>0.1444819770223205</v>
       </c>
       <c r="C60">
-        <v>-81.3761312153914</v>
+        <v>-120.9867569074015</v>
       </c>
       <c r="D60">
-        <v>106.9838687846086</v>
+        <v>70.74324309259848</v>
       </c>
       <c r="E60">
-        <v>69.65999999999998</v>
+        <v>73.02999999999999</v>
       </c>
       <c r="F60">
-        <v>195.46</v>
+        <v>198.83</v>
       </c>
       <c r="G60">
         <v>7.1</v>
@@ -6207,45 +6207,45 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M60">
-        <v>28.693528</v>
+        <v>39.925064</v>
       </c>
       <c r="N60">
-        <v>-5.737972444444445</v>
+        <v>-16.96950844444444</v>
       </c>
       <c r="O60">
-        <v>-1.147594488888889</v>
+        <v>-3.393901688888889</v>
       </c>
       <c r="P60">
-        <v>-4.590377955555556</v>
+        <v>-13.57560675555555</v>
       </c>
       <c r="Q60">
-        <v>4.009622044444442</v>
+        <v>-4.975606755555557</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.0941263806356748</v>
+        <v>0.09666695641335393</v>
       </c>
       <c r="T60">
-        <v>0.9167335829563031</v>
+        <v>0.9649273666580455</v>
       </c>
       <c r="U60">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1600051102503363</v>
+        <v>0.1149932060499918</v>
       </c>
       <c r="W60">
-        <v>0.1233112498152506</v>
+        <v>0.1777093642251616</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.8000255512516814</v>
+        <v>0.5749660302499592</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1444819770223205</v>
+        <v>0.1460319770223205</v>
       </c>
       <c r="C61">
-        <v>-120.9867569074015</v>
+        <v>-125.4507393873551</v>
       </c>
       <c r="D61">
-        <v>70.74324309259848</v>
+        <v>69.64926061264491</v>
       </c>
       <c r="E61">
-        <v>73.02999999999999</v>
+        <v>76.39999999999999</v>
       </c>
       <c r="F61">
-        <v>198.83</v>
+        <v>202.2</v>
       </c>
       <c r="G61">
         <v>7.1</v>
@@ -6289,37 +6289,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M61">
-        <v>39.925064</v>
+        <v>40.60176</v>
       </c>
       <c r="N61">
-        <v>-16.96950844444444</v>
+        <v>-17.64620444444444</v>
       </c>
       <c r="O61">
-        <v>-3.393901688888889</v>
+        <v>-3.529240888888889</v>
       </c>
       <c r="P61">
-        <v>-13.57560675555555</v>
+        <v>-14.11696355555555</v>
       </c>
       <c r="Q61">
-        <v>-4.975606755555557</v>
+        <v>-5.516963555555556</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09666695641335393</v>
+        <v>0.09793863032368777</v>
       </c>
       <c r="T61">
-        <v>0.9649273666580455</v>
+        <v>0.9890505508244964</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1149932060499918</v>
+        <v>0.1130766526158253</v>
       </c>
       <c r="W61">
-        <v>0.1777093642251616</v>
+        <v>0.1780942081547423</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5749660302499592</v>
+        <v>0.5653832630791265</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1460319770223205</v>
+        <v>0.1475819770223205</v>
       </c>
       <c r="C62">
-        <v>-125.4507393873551</v>
+        <v>-129.881402159959</v>
       </c>
       <c r="D62">
-        <v>69.64926061264491</v>
+        <v>68.58859784004102</v>
       </c>
       <c r="E62">
-        <v>76.39999999999999</v>
+        <v>79.77</v>
       </c>
       <c r="F62">
-        <v>202.2</v>
+        <v>205.57</v>
       </c>
       <c r="G62">
         <v>7.1</v>
@@ -6371,37 +6371,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M62">
-        <v>40.60176</v>
+        <v>41.278456</v>
       </c>
       <c r="N62">
-        <v>-17.64620444444444</v>
+        <v>-18.32290044444444</v>
       </c>
       <c r="O62">
-        <v>-3.529240888888889</v>
+        <v>-3.664580088888889</v>
       </c>
       <c r="P62">
-        <v>-14.11696355555555</v>
+        <v>-14.65832035555555</v>
       </c>
       <c r="Q62">
-        <v>-5.516963555555556</v>
+        <v>-6.058320355555557</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09793863032368777</v>
+        <v>0.09927551828070541</v>
       </c>
       <c r="T62">
-        <v>0.9890505508244964</v>
+        <v>1.014410821358458</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1130766526158253</v>
+        <v>0.1112229369991724</v>
       </c>
       <c r="W62">
-        <v>0.1780942081547423</v>
+        <v>0.1784664342505662</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5653832630791265</v>
+        <v>0.5561146849958621</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1475819770223205</v>
+        <v>0.1491319770223205</v>
       </c>
       <c r="C63">
-        <v>-129.881402159959</v>
+        <v>-134.2802446317245</v>
       </c>
       <c r="D63">
-        <v>68.58859784004102</v>
+        <v>67.55975536827549</v>
       </c>
       <c r="E63">
-        <v>79.77</v>
+        <v>83.14</v>
       </c>
       <c r="F63">
-        <v>205.57</v>
+        <v>208.94</v>
       </c>
       <c r="G63">
         <v>7.1</v>
@@ -6453,37 +6453,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M63">
-        <v>41.278456</v>
+        <v>41.955152</v>
       </c>
       <c r="N63">
-        <v>-18.32290044444444</v>
+        <v>-18.99959644444444</v>
       </c>
       <c r="O63">
-        <v>-3.664580088888889</v>
+        <v>-3.799919288888889</v>
       </c>
       <c r="P63">
-        <v>-14.65832035555555</v>
+        <v>-15.19967715555555</v>
       </c>
       <c r="Q63">
-        <v>-6.058320355555557</v>
+        <v>-6.599677155555556</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.09927551828070541</v>
+        <v>0.1006827687617766</v>
       </c>
       <c r="T63">
-        <v>1.014410821358458</v>
+        <v>1.041105842973154</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1112229369991724</v>
+        <v>0.1094290186604761</v>
       </c>
       <c r="W63">
-        <v>0.1784664342505662</v>
+        <v>0.1788266530529764</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5561146849958621</v>
+        <v>0.5471450933023805</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1491319770223205</v>
+        <v>0.1506819770223205</v>
       </c>
       <c r="C64">
-        <v>-134.2802446317245</v>
+        <v>-138.6486775731492</v>
       </c>
       <c r="D64">
-        <v>67.55975536827549</v>
+        <v>66.56132242685082</v>
       </c>
       <c r="E64">
-        <v>83.14</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="F64">
-        <v>208.94</v>
+        <v>212.31</v>
       </c>
       <c r="G64">
         <v>7.1</v>
@@ -6535,37 +6535,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M64">
-        <v>41.955152</v>
+        <v>42.63184800000001</v>
       </c>
       <c r="N64">
-        <v>-18.99959644444444</v>
+        <v>-19.67629244444445</v>
       </c>
       <c r="O64">
-        <v>-3.799919288888889</v>
+        <v>-3.93525848888889</v>
       </c>
       <c r="P64">
-        <v>-15.19967715555555</v>
+        <v>-15.74103395555556</v>
       </c>
       <c r="Q64">
-        <v>-6.599677155555556</v>
+        <v>-7.141033955555562</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1006827687617766</v>
+        <v>0.1021660868364192</v>
       </c>
       <c r="T64">
-        <v>1.041105842973154</v>
+        <v>1.069243838729185</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1094290186604761</v>
+        <v>0.1076920501103098</v>
       </c>
       <c r="W64">
-        <v>0.1788266530529764</v>
+        <v>0.1791754363378498</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5471450933023805</v>
+        <v>0.538460250551549</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1506819770223205</v>
+        <v>0.1522319770223205</v>
       </c>
       <c r="C65">
-        <v>-138.6486775731492</v>
+        <v>-142.9880295728775</v>
       </c>
       <c r="D65">
-        <v>66.56132242685082</v>
+        <v>65.59197042712256</v>
       </c>
       <c r="E65">
-        <v>86.51000000000001</v>
+        <v>89.88000000000001</v>
       </c>
       <c r="F65">
-        <v>212.31</v>
+        <v>215.68</v>
       </c>
       <c r="G65">
         <v>7.1</v>
@@ -6617,37 +6617,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M65">
-        <v>42.63184800000001</v>
+        <v>43.308544</v>
       </c>
       <c r="N65">
-        <v>-19.67629244444445</v>
+        <v>-20.35298844444445</v>
       </c>
       <c r="O65">
-        <v>-3.93525848888889</v>
+        <v>-4.07059768888889</v>
       </c>
       <c r="P65">
-        <v>-15.74103395555556</v>
+        <v>-16.28239075555556</v>
       </c>
       <c r="Q65">
-        <v>-7.141033955555562</v>
+        <v>-7.682390755555563</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1021660868364192</v>
+        <v>0.1037318114707642</v>
       </c>
       <c r="T65">
-        <v>1.069243838729185</v>
+        <v>1.098945056471663</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1076920501103098</v>
+        <v>0.1060093618273362</v>
       </c>
       <c r="W65">
-        <v>0.1791754363378498</v>
+        <v>0.1795133201450709</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.538460250551549</v>
+        <v>0.530046809136681</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1522319770223205</v>
+        <v>0.1537819770223205</v>
       </c>
       <c r="C66">
-        <v>-142.9880295728775</v>
+        <v>-147.2995529359941</v>
       </c>
       <c r="D66">
-        <v>65.59197042712256</v>
+        <v>64.65044706400589</v>
       </c>
       <c r="E66">
-        <v>89.88000000000001</v>
+        <v>93.25000000000001</v>
       </c>
       <c r="F66">
-        <v>215.68</v>
+        <v>219.05</v>
       </c>
       <c r="G66">
         <v>7.1</v>
@@ -6699,37 +6699,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M66">
-        <v>43.308544</v>
+        <v>43.98524</v>
       </c>
       <c r="N66">
-        <v>-20.35298844444445</v>
+        <v>-21.02968444444445</v>
       </c>
       <c r="O66">
-        <v>-4.07059768888889</v>
+        <v>-4.20593688888889</v>
       </c>
       <c r="P66">
-        <v>-16.28239075555556</v>
+        <v>-16.82374755555556</v>
       </c>
       <c r="Q66">
-        <v>-7.682390755555563</v>
+        <v>-8.223747555555562</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1037318114707642</v>
+        <v>0.1053870060842146</v>
       </c>
       <c r="T66">
-        <v>1.098945056471663</v>
+        <v>1.130343486656568</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1060093618273362</v>
+        <v>0.1043784485684541</v>
       </c>
       <c r="W66">
-        <v>0.1795133201450709</v>
+        <v>0.1798408075274544</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.530046809136681</v>
+        <v>0.5218922428422705</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1537819770223205</v>
+        <v>0.1553319770223205</v>
       </c>
       <c r="C67">
-        <v>-147.2995529359941</v>
+        <v>-151.5844290815127</v>
       </c>
       <c r="D67">
-        <v>64.65044706400589</v>
+        <v>63.73557091848735</v>
       </c>
       <c r="E67">
-        <v>93.25000000000001</v>
+        <v>96.62000000000002</v>
       </c>
       <c r="F67">
-        <v>219.05</v>
+        <v>222.42</v>
       </c>
       <c r="G67">
         <v>7.1</v>
@@ -6781,37 +6781,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M67">
-        <v>43.98524</v>
+        <v>44.661936</v>
       </c>
       <c r="N67">
-        <v>-21.02968444444445</v>
+        <v>-21.70638044444445</v>
       </c>
       <c r="O67">
-        <v>-4.20593688888889</v>
+        <v>-4.34127608888889</v>
       </c>
       <c r="P67">
-        <v>-16.82374755555556</v>
+        <v>-17.36510435555556</v>
       </c>
       <c r="Q67">
-        <v>-8.223747555555562</v>
+        <v>-8.765104355555561</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1053870060842146</v>
+        <v>0.1071395650866915</v>
       </c>
       <c r="T67">
-        <v>1.130343486656568</v>
+        <v>1.163588883322937</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1043784485684541</v>
+        <v>0.1027969569234776</v>
       </c>
       <c r="W67">
-        <v>0.1798408075274544</v>
+        <v>0.1801583710497657</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5218922428422705</v>
+        <v>0.5139847846173877</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1553319770223205</v>
+        <v>0.1568819770223205</v>
       </c>
       <c r="C68">
-        <v>-151.5844290815127</v>
+        <v>-155.8437734879757</v>
       </c>
       <c r="D68">
-        <v>63.73557091848735</v>
+        <v>62.84622651202433</v>
       </c>
       <c r="E68">
-        <v>96.62000000000002</v>
+        <v>99.99000000000002</v>
       </c>
       <c r="F68">
-        <v>222.42</v>
+        <v>225.79</v>
       </c>
       <c r="G68">
         <v>7.1</v>
@@ -6863,37 +6863,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M68">
-        <v>44.661936</v>
+        <v>45.338632</v>
       </c>
       <c r="N68">
-        <v>-21.70638044444445</v>
+        <v>-22.38307644444445</v>
       </c>
       <c r="O68">
-        <v>-4.34127608888889</v>
+        <v>-4.476615288888889</v>
       </c>
       <c r="P68">
-        <v>-17.36510435555556</v>
+        <v>-17.90646115555556</v>
       </c>
       <c r="Q68">
-        <v>-8.765104355555561</v>
+        <v>-9.30646115555556</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1071395650866915</v>
+        <v>0.1089983397862882</v>
       </c>
       <c r="T68">
-        <v>1.163588883322937</v>
+        <v>1.198849152514541</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1027969569234776</v>
+        <v>0.1012626739843212</v>
       </c>
       <c r="W68">
-        <v>0.1801583710497657</v>
+        <v>0.1804664550639483</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5139847846173877</v>
+        <v>0.5063133699216058</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1568819770223205</v>
+        <v>0.1824572869746249</v>
       </c>
       <c r="C69">
-        <v>-155.8437734879757</v>
+        <v>-170.9753981913565</v>
       </c>
       <c r="D69">
-        <v>62.84622651202433</v>
+        <v>51.08460180864349</v>
       </c>
       <c r="E69">
-        <v>99.99000000000002</v>
+        <v>103.36</v>
       </c>
       <c r="F69">
-        <v>225.79</v>
+        <v>229.16</v>
       </c>
       <c r="G69">
         <v>7.1</v>
@@ -6945,45 +6945,45 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M69">
-        <v>45.338632</v>
+        <v>54.03592800000001</v>
       </c>
       <c r="N69">
-        <v>-22.38307644444445</v>
+        <v>-31.08037244444445</v>
       </c>
       <c r="O69">
-        <v>-4.476615288888889</v>
+        <v>-6.21607448888889</v>
       </c>
       <c r="P69">
-        <v>-17.90646115555556</v>
+        <v>-24.86429795555556</v>
       </c>
       <c r="Q69">
-        <v>-9.30646115555556</v>
+        <v>-16.26429795555556</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1089983397862882</v>
+        <v>0.1116773815055609</v>
       </c>
       <c r="T69">
-        <v>1.198849152514541</v>
+        <v>1.249669583961984</v>
       </c>
       <c r="U69">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1012626739843212</v>
+        <v>0.08496404671927002</v>
       </c>
       <c r="W69">
-        <v>0.1804664550639483</v>
+        <v>0.2157654777835961</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.5063133699216058</v>
+        <v>0.42482023359635</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1824572869746249</v>
+        <v>0.1843572869746249</v>
       </c>
       <c r="C70">
-        <v>-170.9753981913565</v>
+        <v>-175.0459080350157</v>
       </c>
       <c r="D70">
-        <v>51.08460180864349</v>
+        <v>50.38409196498438</v>
       </c>
       <c r="E70">
-        <v>103.36</v>
+        <v>106.73</v>
       </c>
       <c r="F70">
-        <v>229.16</v>
+        <v>232.53</v>
       </c>
       <c r="G70">
         <v>7.1</v>
@@ -7027,37 +7027,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M70">
-        <v>54.03592800000001</v>
+        <v>54.83057400000001</v>
       </c>
       <c r="N70">
-        <v>-31.08037244444445</v>
+        <v>-31.87501844444445</v>
       </c>
       <c r="O70">
-        <v>-6.21607448888889</v>
+        <v>-6.37500368888889</v>
       </c>
       <c r="P70">
-        <v>-24.86429795555556</v>
+        <v>-25.50001475555556</v>
       </c>
       <c r="Q70">
-        <v>-16.26429795555556</v>
+        <v>-16.90001475555556</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1116773815055609</v>
+        <v>0.113802458328321</v>
       </c>
       <c r="T70">
-        <v>1.249669583961984</v>
+        <v>1.289981506025274</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.08496404671927002</v>
+        <v>0.08373268372333857</v>
       </c>
       <c r="W70">
-        <v>0.2157654777835961</v>
+        <v>0.2160558331780368</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.42482023359635</v>
+        <v>0.4186634186166929</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1843572869746249</v>
+        <v>0.1862572869746249</v>
       </c>
       <c r="C71">
-        <v>-175.0459080350157</v>
+        <v>-179.0974659434406</v>
       </c>
       <c r="D71">
-        <v>50.38409196498438</v>
+        <v>49.70253405655942</v>
       </c>
       <c r="E71">
-        <v>106.73</v>
+        <v>110.1</v>
       </c>
       <c r="F71">
-        <v>232.53</v>
+        <v>235.9</v>
       </c>
       <c r="G71">
         <v>7.1</v>
@@ -7109,37 +7109,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M71">
-        <v>54.83057400000001</v>
+        <v>55.62522000000001</v>
       </c>
       <c r="N71">
-        <v>-31.87501844444445</v>
+        <v>-32.66966444444446</v>
       </c>
       <c r="O71">
-        <v>-6.37500368888889</v>
+        <v>-6.533932888888891</v>
       </c>
       <c r="P71">
-        <v>-25.50001475555556</v>
+        <v>-26.13573155555557</v>
       </c>
       <c r="Q71">
-        <v>-16.90001475555556</v>
+        <v>-17.53573155555557</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.113802458328321</v>
+        <v>0.116069206939265</v>
       </c>
       <c r="T71">
-        <v>1.289981506025274</v>
+        <v>1.332980889559449</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.08373268372333857</v>
+        <v>0.08253650252729086</v>
       </c>
       <c r="W71">
-        <v>0.2160558331780368</v>
+        <v>0.2163378927040648</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4186634186166929</v>
+        <v>0.4126825126364543</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1862572869746249</v>
+        <v>0.1881572869746249</v>
       </c>
       <c r="C72">
-        <v>-179.0974659434406</v>
+        <v>-183.1308307540126</v>
       </c>
       <c r="D72">
-        <v>49.70253405655942</v>
+        <v>49.03916924598742</v>
       </c>
       <c r="E72">
-        <v>110.1</v>
+        <v>113.47</v>
       </c>
       <c r="F72">
-        <v>235.9</v>
+        <v>239.27</v>
       </c>
       <c r="G72">
         <v>7.1</v>
@@ -7191,37 +7191,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M72">
-        <v>55.62522000000001</v>
+        <v>56.41986600000001</v>
       </c>
       <c r="N72">
-        <v>-32.66966444444446</v>
+        <v>-33.46431044444446</v>
       </c>
       <c r="O72">
-        <v>-6.533932888888891</v>
+        <v>-6.692862088888892</v>
       </c>
       <c r="P72">
-        <v>-26.13573155555557</v>
+        <v>-26.77144835555557</v>
       </c>
       <c r="Q72">
-        <v>-17.53573155555557</v>
+        <v>-18.17144835555557</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.116069206939265</v>
+        <v>0.118492283040619</v>
       </c>
       <c r="T72">
-        <v>1.332980889559449</v>
+        <v>1.37894574782012</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08253650252729086</v>
+        <v>0.08137401657620226</v>
       </c>
       <c r="W72">
-        <v>0.2163378927040648</v>
+        <v>0.2166120068913315</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4126825126364543</v>
+        <v>0.4068700828810112</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1881572869746249</v>
+        <v>0.1900572869746249</v>
       </c>
       <c r="C73">
-        <v>-183.1308307540125</v>
+        <v>-187.1467213257919</v>
       </c>
       <c r="D73">
-        <v>49.03916924598746</v>
+        <v>48.39327867420813</v>
       </c>
       <c r="E73">
-        <v>113.47</v>
+        <v>116.84</v>
       </c>
       <c r="F73">
-        <v>239.27</v>
+        <v>242.64</v>
       </c>
       <c r="G73">
         <v>7.1</v>
@@ -7273,37 +7273,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M73">
-        <v>56.419866</v>
+        <v>57.214512</v>
       </c>
       <c r="N73">
-        <v>-33.46431044444444</v>
+        <v>-34.25895644444444</v>
       </c>
       <c r="O73">
-        <v>-6.692862088888889</v>
+        <v>-6.851791288888889</v>
       </c>
       <c r="P73">
-        <v>-26.77144835555556</v>
+        <v>-27.40716515555555</v>
       </c>
       <c r="Q73">
-        <v>-18.17144835555556</v>
+        <v>-18.80716515555556</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.118492283040619</v>
+        <v>0.1210884360063554</v>
       </c>
       <c r="T73">
-        <v>1.37894574782012</v>
+        <v>1.428193810242267</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08137401657620229</v>
+        <v>0.0802438219015328</v>
       </c>
       <c r="W73">
-        <v>0.2166120068913315</v>
+        <v>0.2168785067956186</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4068700828810113</v>
+        <v>0.401219109507664</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1900572869746249</v>
+        <v>0.1919572869746249</v>
       </c>
       <c r="C74">
-        <v>-187.1467213257919</v>
+        <v>-191.1458191380478</v>
       </c>
       <c r="D74">
-        <v>48.39327867420813</v>
+        <v>47.76418086195222</v>
       </c>
       <c r="E74">
-        <v>116.84</v>
+        <v>120.21</v>
       </c>
       <c r="F74">
-        <v>242.64</v>
+        <v>246.01</v>
       </c>
       <c r="G74">
         <v>7.1</v>
@@ -7355,37 +7355,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M74">
-        <v>57.214512</v>
+        <v>58.009158</v>
       </c>
       <c r="N74">
-        <v>-34.25895644444444</v>
+        <v>-35.05360244444444</v>
       </c>
       <c r="O74">
-        <v>-6.851791288888889</v>
+        <v>-7.010720488888889</v>
       </c>
       <c r="P74">
-        <v>-27.40716515555555</v>
+        <v>-28.04288195555555</v>
       </c>
       <c r="Q74">
-        <v>-18.80716515555556</v>
+        <v>-19.44288195555556</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1210884360063554</v>
+        <v>0.1238768965991833</v>
       </c>
       <c r="T74">
-        <v>1.428193810242267</v>
+        <v>1.481089877288277</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0802438219015328</v>
+        <v>0.07914459146452552</v>
       </c>
       <c r="W74">
-        <v>0.2168785067956186</v>
+        <v>0.2171377053326649</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.401219109507664</v>
+        <v>0.3957229573226275</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1919572869746249</v>
+        <v>0.1938572869746249</v>
       </c>
       <c r="C75">
-        <v>-191.1458191380478</v>
+        <v>-195.1287706887085</v>
       </c>
       <c r="D75">
-        <v>47.76418086195222</v>
+        <v>47.15122931129149</v>
       </c>
       <c r="E75">
-        <v>120.21</v>
+        <v>123.58</v>
       </c>
       <c r="F75">
-        <v>246.01</v>
+        <v>249.38</v>
       </c>
       <c r="G75">
         <v>7.1</v>
@@ -7437,37 +7437,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M75">
-        <v>58.009158</v>
+        <v>58.803804</v>
       </c>
       <c r="N75">
-        <v>-35.05360244444444</v>
+        <v>-35.84824844444444</v>
       </c>
       <c r="O75">
-        <v>-7.010720488888889</v>
+        <v>-7.169649688888889</v>
       </c>
       <c r="P75">
-        <v>-28.04288195555555</v>
+        <v>-28.67859875555556</v>
       </c>
       <c r="Q75">
-        <v>-19.44288195555556</v>
+        <v>-20.07859875555556</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1238768965991833</v>
+        <v>0.1268798541606904</v>
       </c>
       <c r="T75">
-        <v>1.481089877288277</v>
+        <v>1.538054872568595</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07914459146452552</v>
+        <v>0.07807506995824814</v>
       </c>
       <c r="W75">
-        <v>0.2171377053326649</v>
+        <v>0.2173898985038451</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3957229573226275</v>
+        <v>0.3903753497912407</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1938572869746249</v>
+        <v>0.1957572869746249</v>
       </c>
       <c r="C76">
-        <v>-195.1287706887085</v>
+        <v>-199.0961897104771</v>
       </c>
       <c r="D76">
-        <v>47.15122931129149</v>
+        <v>46.55381028952295</v>
       </c>
       <c r="E76">
-        <v>123.58</v>
+        <v>126.95</v>
       </c>
       <c r="F76">
-        <v>249.38</v>
+        <v>252.75</v>
       </c>
       <c r="G76">
         <v>7.1</v>
@@ -7519,37 +7519,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M76">
-        <v>58.803804</v>
+        <v>59.59845</v>
       </c>
       <c r="N76">
-        <v>-35.84824844444444</v>
+        <v>-36.64289444444444</v>
       </c>
       <c r="O76">
-        <v>-7.169649688888889</v>
+        <v>-7.328578888888889</v>
       </c>
       <c r="P76">
-        <v>-28.67859875555556</v>
+        <v>-29.31431555555556</v>
       </c>
       <c r="Q76">
-        <v>-20.07859875555556</v>
+        <v>-20.71431555555556</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1268798541606904</v>
+        <v>0.130123048327118</v>
       </c>
       <c r="T76">
-        <v>1.538054872568595</v>
+        <v>1.599577067471339</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07807506995824814</v>
+        <v>0.0770340690254715</v>
       </c>
       <c r="W76">
-        <v>0.2173898985038451</v>
+        <v>0.2176353665237938</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3903753497912407</v>
+        <v>0.3851703451273575</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1957572869746249</v>
+        <v>0.1976572869746249</v>
       </c>
       <c r="C77">
-        <v>-199.0961897104771</v>
+        <v>-203.0486592205828</v>
       </c>
       <c r="D77">
-        <v>46.55381028952295</v>
+        <v>45.97134077941722</v>
       </c>
       <c r="E77">
-        <v>126.95</v>
+        <v>130.32</v>
       </c>
       <c r="F77">
-        <v>252.75</v>
+        <v>256.12</v>
       </c>
       <c r="G77">
         <v>7.1</v>
@@ -7601,37 +7601,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M77">
-        <v>59.59845</v>
+        <v>60.39309600000001</v>
       </c>
       <c r="N77">
-        <v>-36.64289444444444</v>
+        <v>-37.43754044444445</v>
       </c>
       <c r="O77">
-        <v>-7.328578888888889</v>
+        <v>-7.487508088888891</v>
       </c>
       <c r="P77">
-        <v>-29.31431555555556</v>
+        <v>-29.95003235555556</v>
       </c>
       <c r="Q77">
-        <v>-20.71431555555556</v>
+        <v>-21.35003235555556</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.130123048327118</v>
+        <v>0.1336365086740813</v>
       </c>
       <c r="T77">
-        <v>1.599577067471339</v>
+        <v>1.666226111949312</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0770340690254715</v>
+        <v>0.0760204628540837</v>
       </c>
       <c r="W77">
-        <v>0.2176353665237938</v>
+        <v>0.2178743748590071</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3851703451273575</v>
+        <v>0.3801023142704185</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1976572869746249</v>
+        <v>0.1995572869746249</v>
       </c>
       <c r="C78">
-        <v>-203.0486592205828</v>
+        <v>-206.9867334185576</v>
       </c>
       <c r="D78">
-        <v>45.97134077941722</v>
+        <v>45.40326658144239</v>
       </c>
       <c r="E78">
-        <v>130.32</v>
+        <v>133.69</v>
       </c>
       <c r="F78">
-        <v>256.12</v>
+        <v>259.49</v>
       </c>
       <c r="G78">
         <v>7.1</v>
@@ -7683,37 +7683,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M78">
-        <v>60.39309600000001</v>
+        <v>61.18774200000001</v>
       </c>
       <c r="N78">
-        <v>-37.43754044444445</v>
+        <v>-38.23218644444445</v>
       </c>
       <c r="O78">
-        <v>-7.487508088888891</v>
+        <v>-7.64643728888889</v>
       </c>
       <c r="P78">
-        <v>-29.95003235555556</v>
+        <v>-30.58574915555556</v>
       </c>
       <c r="Q78">
-        <v>-21.35003235555556</v>
+        <v>-21.98574915555556</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1336365086740813</v>
+        <v>0.1374554873120848</v>
       </c>
       <c r="T78">
-        <v>1.666226111949312</v>
+        <v>1.738670725512325</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.0760204628540837</v>
+        <v>0.07503318411571898</v>
       </c>
       <c r="W78">
-        <v>0.2178743748590071</v>
+        <v>0.2181071751855135</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3801023142704185</v>
+        <v>0.3751659205785949</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1995572869746249</v>
+        <v>0.2014572869746249</v>
       </c>
       <c r="C79">
-        <v>-206.9867334185576</v>
+        <v>-210.910939445024</v>
       </c>
       <c r="D79">
-        <v>45.40326658144239</v>
+        <v>44.84906055497606</v>
       </c>
       <c r="E79">
-        <v>133.69</v>
+        <v>137.06</v>
       </c>
       <c r="F79">
-        <v>259.49</v>
+        <v>262.86</v>
       </c>
       <c r="G79">
         <v>7.1</v>
@@ -7765,37 +7765,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M79">
-        <v>61.18774200000001</v>
+        <v>61.98238800000001</v>
       </c>
       <c r="N79">
-        <v>-38.23218644444445</v>
+        <v>-39.02683244444445</v>
       </c>
       <c r="O79">
-        <v>-7.64643728888889</v>
+        <v>-7.805366488888891</v>
       </c>
       <c r="P79">
-        <v>-30.58574915555556</v>
+        <v>-31.22146595555556</v>
       </c>
       <c r="Q79">
-        <v>-21.98574915555556</v>
+        <v>-22.62146595555556</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1374554873120848</v>
+        <v>0.1416216458262705</v>
       </c>
       <c r="T79">
-        <v>1.738670725512325</v>
+        <v>1.817701213035613</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07503318411571898</v>
+        <v>0.0740712202167995</v>
       </c>
       <c r="W79">
-        <v>0.2181071751855135</v>
+        <v>0.2183340062728787</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3751659205785949</v>
+        <v>0.3703561010839975</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2014572869746249</v>
+        <v>0.2033572869746249</v>
       </c>
       <c r="C80">
-        <v>-210.910939445024</v>
+        <v>-214.8217790132261</v>
       </c>
       <c r="D80">
-        <v>44.84906055497606</v>
+        <v>44.30822098677388</v>
       </c>
       <c r="E80">
-        <v>137.06</v>
+        <v>140.43</v>
       </c>
       <c r="F80">
-        <v>262.86</v>
+        <v>266.23</v>
       </c>
       <c r="G80">
         <v>7.1</v>
@@ -7847,37 +7847,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M80">
-        <v>61.98238800000001</v>
+        <v>62.77703400000001</v>
       </c>
       <c r="N80">
-        <v>-39.02683244444445</v>
+        <v>-39.82147844444445</v>
       </c>
       <c r="O80">
-        <v>-7.805366488888891</v>
+        <v>-7.964295688888891</v>
       </c>
       <c r="P80">
-        <v>-31.22146595555556</v>
+        <v>-31.85718275555556</v>
       </c>
       <c r="Q80">
-        <v>-22.62146595555556</v>
+        <v>-23.25718275555557</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1416216458262705</v>
+        <v>0.1461845813418072</v>
       </c>
       <c r="T80">
-        <v>1.817701213035613</v>
+        <v>1.904258413656356</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0740712202167995</v>
+        <v>0.07313360983430837</v>
       </c>
       <c r="W80">
-        <v>0.2183340062728787</v>
+        <v>0.2185550948010701</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3703561010839975</v>
+        <v>0.3656680491715418</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2033572869746249</v>
+        <v>0.2052572869746249</v>
       </c>
       <c r="C81">
-        <v>-214.8217790132261</v>
+        <v>-218.719729923919</v>
       </c>
       <c r="D81">
-        <v>44.30822098677388</v>
+        <v>43.78027007608104</v>
       </c>
       <c r="E81">
-        <v>140.43</v>
+        <v>143.8</v>
       </c>
       <c r="F81">
-        <v>266.23</v>
+        <v>269.6</v>
       </c>
       <c r="G81">
         <v>7.1</v>
@@ -7929,37 +7929,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M81">
-        <v>62.77703400000001</v>
+        <v>63.57168000000001</v>
       </c>
       <c r="N81">
-        <v>-39.82147844444445</v>
+        <v>-40.61612444444445</v>
       </c>
       <c r="O81">
-        <v>-7.964295688888891</v>
+        <v>-8.12322488888889</v>
       </c>
       <c r="P81">
-        <v>-31.85718275555556</v>
+        <v>-32.49289955555556</v>
       </c>
       <c r="Q81">
-        <v>-23.25718275555557</v>
+        <v>-23.89289955555556</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1461845813418072</v>
+        <v>0.1512038104088975</v>
       </c>
       <c r="T81">
-        <v>1.904258413656356</v>
+        <v>1.999471334339174</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07313360983430837</v>
+        <v>0.07221943971137951</v>
       </c>
       <c r="W81">
-        <v>0.2185550948010701</v>
+        <v>0.2187706561160567</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3656680491715418</v>
+        <v>0.3610971985568976</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2052572869746249</v>
+        <v>0.2071572869746249</v>
       </c>
       <c r="C82">
-        <v>-218.719729923919</v>
+        <v>-222.6052474732295</v>
       </c>
       <c r="D82">
-        <v>43.78027007608104</v>
+        <v>43.26475252677051</v>
       </c>
       <c r="E82">
-        <v>143.8</v>
+        <v>147.17</v>
       </c>
       <c r="F82">
-        <v>269.6</v>
+        <v>272.97</v>
       </c>
       <c r="G82">
         <v>7.1</v>
@@ -8011,37 +8011,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M82">
-        <v>63.57168000000001</v>
+        <v>64.36632600000002</v>
       </c>
       <c r="N82">
-        <v>-40.61612444444445</v>
+        <v>-41.41077044444446</v>
       </c>
       <c r="O82">
-        <v>-8.12322488888889</v>
+        <v>-8.282154088888893</v>
       </c>
       <c r="P82">
-        <v>-32.49289955555556</v>
+        <v>-33.12861635555556</v>
       </c>
       <c r="Q82">
-        <v>-23.89289955555556</v>
+        <v>-24.52861635555557</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1512038104088975</v>
+        <v>0.1567513793777869</v>
       </c>
       <c r="T82">
-        <v>1.999471334339174</v>
+        <v>2.104706667725446</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07221943971137951</v>
+        <v>0.07132784169025136</v>
       </c>
       <c r="W82">
-        <v>0.2187706561160567</v>
+        <v>0.2189808949294387</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3610971985568976</v>
+        <v>0.3566392084512569</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2071572869746249</v>
+        <v>0.2090572869746249</v>
       </c>
       <c r="C83">
-        <v>-222.6052474732295</v>
+        <v>-226.4787657622089</v>
       </c>
       <c r="D83">
-        <v>43.26475252677051</v>
+        <v>42.76123423779116</v>
       </c>
       <c r="E83">
-        <v>147.17</v>
+        <v>150.54</v>
       </c>
       <c r="F83">
-        <v>272.97</v>
+        <v>276.34</v>
       </c>
       <c r="G83">
         <v>7.1</v>
@@ -8093,37 +8093,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M83">
-        <v>64.36632600000002</v>
+        <v>65.16097200000002</v>
       </c>
       <c r="N83">
-        <v>-41.41077044444446</v>
+        <v>-42.20541644444446</v>
       </c>
       <c r="O83">
-        <v>-8.282154088888893</v>
+        <v>-8.441083288888892</v>
       </c>
       <c r="P83">
-        <v>-33.12861635555556</v>
+        <v>-33.76433315555557</v>
       </c>
       <c r="Q83">
-        <v>-24.52861635555557</v>
+        <v>-25.16433315555557</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1567513793777869</v>
+        <v>0.1629153448987751</v>
       </c>
       <c r="T83">
-        <v>2.104706667725446</v>
+        <v>2.221634815932416</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07132784169025136</v>
+        <v>0.07045798996232147</v>
       </c>
       <c r="W83">
-        <v>0.2189808949294387</v>
+        <v>0.2191860059668846</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3566392084512569</v>
+        <v>0.3522899498116073</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2090572869746249</v>
+        <v>0.2109572869746249</v>
       </c>
       <c r="C84">
-        <v>-226.4787657622089</v>
+        <v>-230.3406989159926</v>
       </c>
       <c r="D84">
-        <v>42.76123423779116</v>
+        <v>42.26930108400739</v>
       </c>
       <c r="E84">
-        <v>150.54</v>
+        <v>153.91</v>
       </c>
       <c r="F84">
-        <v>276.34</v>
+        <v>279.71</v>
       </c>
       <c r="G84">
         <v>7.1</v>
@@ -8175,37 +8175,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M84">
-        <v>65.16097200000002</v>
+        <v>65.95561800000002</v>
       </c>
       <c r="N84">
-        <v>-42.20541644444446</v>
+        <v>-43.00006244444446</v>
       </c>
       <c r="O84">
-        <v>-8.441083288888892</v>
+        <v>-8.600012488888892</v>
       </c>
       <c r="P84">
-        <v>-33.76433315555557</v>
+        <v>-34.40004995555557</v>
       </c>
       <c r="Q84">
-        <v>-25.16433315555557</v>
+        <v>-25.80004995555557</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1629153448987751</v>
+        <v>0.1698044828339971</v>
       </c>
       <c r="T84">
-        <v>2.221634815932416</v>
+        <v>2.352319216869617</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07045798996232147</v>
+        <v>0.0696090985169923</v>
       </c>
       <c r="W84">
-        <v>0.2191860059668846</v>
+        <v>0.2193861745696932</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3522899498116073</v>
+        <v>0.3480454925849614</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2109572869746249</v>
+        <v>0.2128572869746249</v>
       </c>
       <c r="C85">
-        <v>-230.3406989159926</v>
+        <v>-234.1914422197661</v>
       </c>
       <c r="D85">
-        <v>42.26930108400739</v>
+        <v>41.78855778023397</v>
       </c>
       <c r="E85">
-        <v>153.91</v>
+        <v>157.28</v>
       </c>
       <c r="F85">
-        <v>279.71</v>
+        <v>283.08</v>
       </c>
       <c r="G85">
         <v>7.1</v>
@@ -8257,37 +8257,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M85">
-        <v>65.95561800000002</v>
+        <v>66.75026400000002</v>
       </c>
       <c r="N85">
-        <v>-43.00006244444446</v>
+        <v>-43.79470844444446</v>
       </c>
       <c r="O85">
-        <v>-8.600012488888892</v>
+        <v>-8.758941688888893</v>
       </c>
       <c r="P85">
-        <v>-34.40004995555557</v>
+        <v>-35.03576675555557</v>
       </c>
       <c r="Q85">
-        <v>-25.80004995555557</v>
+        <v>-26.43576675555557</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1698044828339971</v>
+        <v>0.177554763011122</v>
       </c>
       <c r="T85">
-        <v>2.352319216869617</v>
+        <v>2.499339167923969</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0696090985169923</v>
+        <v>0.06878041877274238</v>
       </c>
       <c r="W85">
-        <v>0.2193861745696932</v>
+        <v>0.2195815772533874</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3480454925849614</v>
+        <v>0.343902093863712</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2128572869746249</v>
+        <v>0.2147572869746249</v>
       </c>
       <c r="C86">
-        <v>-234.191442219766</v>
+        <v>-238.0313731780819</v>
       </c>
       <c r="D86">
-        <v>41.78855778023397</v>
+        <v>41.31862682191805</v>
       </c>
       <c r="E86">
-        <v>157.28</v>
+        <v>160.65</v>
       </c>
       <c r="F86">
-        <v>283.08</v>
+        <v>286.45</v>
       </c>
       <c r="G86">
         <v>7.1</v>
@@ -8339,37 +8339,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M86">
-        <v>66.750264</v>
+        <v>67.54491</v>
       </c>
       <c r="N86">
-        <v>-43.79470844444445</v>
+        <v>-44.58935444444445</v>
       </c>
       <c r="O86">
-        <v>-8.758941688888889</v>
+        <v>-8.91787088888889</v>
       </c>
       <c r="P86">
-        <v>-35.03576675555556</v>
+        <v>-35.67148355555555</v>
       </c>
       <c r="Q86">
-        <v>-26.43576675555556</v>
+        <v>-27.07148355555556</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1775547630111219</v>
+        <v>0.18633841387853</v>
       </c>
       <c r="T86">
-        <v>2.499339167923967</v>
+        <v>2.665961779118898</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06878041877274241</v>
+        <v>0.06797123737541602</v>
       </c>
       <c r="W86">
-        <v>0.2195815772533873</v>
+        <v>0.2197723822268769</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.343902093863712</v>
+        <v>0.3398561868770801</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2147572869746249</v>
+        <v>0.2166572869746249</v>
       </c>
       <c r="C87">
-        <v>-238.0313731780819</v>
+        <v>-241.8608525034988</v>
       </c>
       <c r="D87">
-        <v>41.31862682191805</v>
+        <v>40.85914749650119</v>
       </c>
       <c r="E87">
-        <v>160.65</v>
+        <v>164.02</v>
       </c>
       <c r="F87">
-        <v>286.45</v>
+        <v>289.82</v>
       </c>
       <c r="G87">
         <v>7.1</v>
@@ -8421,37 +8421,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M87">
-        <v>67.54491</v>
+        <v>68.339556</v>
       </c>
       <c r="N87">
-        <v>-44.58935444444445</v>
+        <v>-45.38400044444445</v>
       </c>
       <c r="O87">
-        <v>-8.91787088888889</v>
+        <v>-9.07680008888889</v>
       </c>
       <c r="P87">
-        <v>-35.67148355555555</v>
+        <v>-36.30720035555556</v>
       </c>
       <c r="Q87">
-        <v>-27.07148355555556</v>
+        <v>-27.70720035555556</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.18633841387853</v>
+        <v>0.1963768720127107</v>
       </c>
       <c r="T87">
-        <v>2.665961779118898</v>
+        <v>2.856387620484534</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06797123737541602</v>
+        <v>0.06718087415012049</v>
       </c>
       <c r="W87">
-        <v>0.2197723822268769</v>
+        <v>0.2199587498754016</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3398561868770801</v>
+        <v>0.3359043707506024</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2166572869746249</v>
+        <v>0.2185572869746249</v>
       </c>
       <c r="C88">
-        <v>-241.8608525034988</v>
+        <v>-245.6802250399797</v>
       </c>
       <c r="D88">
-        <v>40.85914749650119</v>
+        <v>40.40977496002024</v>
       </c>
       <c r="E88">
-        <v>164.02</v>
+        <v>167.39</v>
       </c>
       <c r="F88">
-        <v>289.82</v>
+        <v>293.19</v>
       </c>
       <c r="G88">
         <v>7.1</v>
@@ -8503,37 +8503,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M88">
-        <v>68.339556</v>
+        <v>69.134202</v>
       </c>
       <c r="N88">
-        <v>-45.38400044444445</v>
+        <v>-46.17864644444445</v>
       </c>
       <c r="O88">
-        <v>-9.07680008888889</v>
+        <v>-9.235729288888889</v>
       </c>
       <c r="P88">
-        <v>-36.30720035555556</v>
+        <v>-36.94291715555556</v>
       </c>
       <c r="Q88">
-        <v>-27.70720035555556</v>
+        <v>-28.34291715555556</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1963768720127107</v>
+        <v>0.2079597083213808</v>
       </c>
       <c r="T88">
-        <v>2.856387620484534</v>
+        <v>3.07610974513719</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06718087415012049</v>
+        <v>0.06640868019437197</v>
       </c>
       <c r="W88">
-        <v>0.2199587498754016</v>
+        <v>0.2201408332101671</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3359043707506024</v>
+        <v>0.3320434009718598</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2185572869746249</v>
+        <v>0.2204572869746249</v>
       </c>
       <c r="C89">
-        <v>-245.6802250399797</v>
+        <v>-249.4898206260213</v>
       </c>
       <c r="D89">
-        <v>40.40977496002024</v>
+        <v>39.9701793739787</v>
       </c>
       <c r="E89">
-        <v>167.39</v>
+        <v>170.76</v>
       </c>
       <c r="F89">
-        <v>293.19</v>
+        <v>296.56</v>
       </c>
       <c r="G89">
         <v>7.1</v>
@@ -8585,37 +8585,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M89">
-        <v>69.134202</v>
+        <v>69.928848</v>
       </c>
       <c r="N89">
-        <v>-46.17864644444445</v>
+        <v>-46.97329244444445</v>
       </c>
       <c r="O89">
-        <v>-9.235729288888889</v>
+        <v>-9.39465848888889</v>
       </c>
       <c r="P89">
-        <v>-36.94291715555556</v>
+        <v>-37.57863395555556</v>
       </c>
       <c r="Q89">
-        <v>-28.34291715555556</v>
+        <v>-28.97863395555556</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2079597083213808</v>
+        <v>0.2214730173481625</v>
       </c>
       <c r="T89">
-        <v>3.07610974513719</v>
+        <v>3.332452223898623</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06640868019437197</v>
+        <v>0.06565403610125412</v>
       </c>
       <c r="W89">
-        <v>0.2201408332101671</v>
+        <v>0.2203187782873243</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3320434009718598</v>
+        <v>0.3282701805062705</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2204572869746249</v>
+        <v>0.2223572869746249</v>
       </c>
       <c r="C90">
-        <v>-249.4898206260213</v>
+        <v>-253.2899549020507</v>
       </c>
       <c r="D90">
-        <v>39.9701793739787</v>
+        <v>39.54004509794927</v>
       </c>
       <c r="E90">
-        <v>170.76</v>
+        <v>174.13</v>
       </c>
       <c r="F90">
-        <v>296.56</v>
+        <v>299.93</v>
       </c>
       <c r="G90">
         <v>7.1</v>
@@ -8667,37 +8667,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M90">
-        <v>69.928848</v>
+        <v>70.723494</v>
       </c>
       <c r="N90">
-        <v>-46.97329244444445</v>
+        <v>-47.76793844444445</v>
       </c>
       <c r="O90">
-        <v>-9.39465848888889</v>
+        <v>-9.553587688888889</v>
       </c>
       <c r="P90">
-        <v>-37.57863395555556</v>
+        <v>-38.21435075555556</v>
       </c>
       <c r="Q90">
-        <v>-28.97863395555556</v>
+        <v>-29.61435075555556</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2214730173481625</v>
+        <v>0.237443291652541</v>
       </c>
       <c r="T90">
-        <v>3.332452223898623</v>
+        <v>3.635402426071225</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06565403610125412</v>
+        <v>0.06491635030236362</v>
       </c>
       <c r="W90">
-        <v>0.2203187782873243</v>
+        <v>0.2204927245987027</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3282701805062705</v>
+        <v>0.324581751511818</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2223572869746249</v>
+        <v>0.2242572869746249</v>
       </c>
       <c r="C91">
-        <v>-253.2899549020507</v>
+        <v>-257.0809300662467</v>
       </c>
       <c r="D91">
-        <v>39.54004509794927</v>
+        <v>39.11906993375332</v>
       </c>
       <c r="E91">
-        <v>174.13</v>
+        <v>177.5</v>
       </c>
       <c r="F91">
-        <v>299.93</v>
+        <v>303.3</v>
       </c>
       <c r="G91">
         <v>7.1</v>
@@ -8749,37 +8749,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M91">
-        <v>70.723494</v>
+        <v>71.51814</v>
       </c>
       <c r="N91">
-        <v>-47.76793844444445</v>
+        <v>-48.56258444444445</v>
       </c>
       <c r="O91">
-        <v>-9.553587688888889</v>
+        <v>-9.71251688888889</v>
       </c>
       <c r="P91">
-        <v>-38.21435075555556</v>
+        <v>-38.85006755555555</v>
       </c>
       <c r="Q91">
-        <v>-29.61435075555556</v>
+        <v>-30.25006755555556</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.237443291652541</v>
+        <v>0.256607620817795</v>
       </c>
       <c r="T91">
-        <v>3.635402426071225</v>
+        <v>3.998942668678348</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06491635030236362</v>
+        <v>0.06419505752122624</v>
       </c>
       <c r="W91">
-        <v>0.2204927245987027</v>
+        <v>0.2206628054364949</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.324581751511818</v>
+        <v>0.3209752876061311</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2242572869746249</v>
+        <v>0.2261572869746249</v>
       </c>
       <c r="C92">
-        <v>-257.0809300662467</v>
+        <v>-260.8630355825854</v>
       </c>
       <c r="D92">
-        <v>39.11906993375332</v>
+        <v>38.70696441741455</v>
       </c>
       <c r="E92">
-        <v>177.5</v>
+        <v>180.87</v>
       </c>
       <c r="F92">
-        <v>303.3</v>
+        <v>306.67</v>
       </c>
       <c r="G92">
         <v>7.1</v>
@@ -8831,37 +8831,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M92">
-        <v>71.51814</v>
+        <v>72.312786</v>
       </c>
       <c r="N92">
-        <v>-48.56258444444445</v>
+        <v>-49.35723044444445</v>
       </c>
       <c r="O92">
-        <v>-9.71251688888889</v>
+        <v>-9.87144608888889</v>
       </c>
       <c r="P92">
-        <v>-38.85006755555555</v>
+        <v>-39.48578435555556</v>
       </c>
       <c r="Q92">
-        <v>-30.25006755555556</v>
+        <v>-30.88578435555556</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.256607620817795</v>
+        <v>0.2800306897975501</v>
       </c>
       <c r="T92">
-        <v>3.998942668678348</v>
+        <v>4.443269631864831</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06419505752122624</v>
+        <v>0.06348961732868529</v>
       </c>
       <c r="W92">
-        <v>0.2206628054364949</v>
+        <v>0.220829148233896</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3209752876061311</v>
+        <v>0.3174480866434265</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2261572869746249</v>
+        <v>0.2280572869746249</v>
       </c>
       <c r="C93">
-        <v>-260.8630355825854</v>
+        <v>-264.6365488446002</v>
       </c>
       <c r="D93">
-        <v>38.70696441741455</v>
+        <v>38.30345115539984</v>
       </c>
       <c r="E93">
-        <v>180.87</v>
+        <v>184.24</v>
       </c>
       <c r="F93">
-        <v>306.67</v>
+        <v>310.04</v>
       </c>
       <c r="G93">
         <v>7.1</v>
@@ -8913,37 +8913,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M93">
-        <v>72.312786</v>
+        <v>73.107432</v>
       </c>
       <c r="N93">
-        <v>-49.35723044444445</v>
+        <v>-50.15187644444445</v>
       </c>
       <c r="O93">
-        <v>-9.87144608888889</v>
+        <v>-10.03037528888889</v>
       </c>
       <c r="P93">
-        <v>-39.48578435555556</v>
+        <v>-40.12150115555556</v>
       </c>
       <c r="Q93">
-        <v>-30.88578435555556</v>
+        <v>-31.52150115555556</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2800306897975501</v>
+        <v>0.3093095260222439</v>
       </c>
       <c r="T93">
-        <v>4.443269631864831</v>
+        <v>4.998678335847937</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06348961732868529</v>
+        <v>0.06279951279250394</v>
       </c>
       <c r="W93">
-        <v>0.220829148233896</v>
+        <v>0.2209918748835276</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3174480866434265</v>
+        <v>0.3139975639625197</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2280572869746249</v>
+        <v>0.2299572869746249</v>
       </c>
       <c r="C94">
-        <v>-264.6365488446002</v>
+        <v>-268.401735798051</v>
       </c>
       <c r="D94">
-        <v>38.30345115539984</v>
+        <v>37.90826420194905</v>
       </c>
       <c r="E94">
-        <v>184.24</v>
+        <v>187.61</v>
       </c>
       <c r="F94">
-        <v>310.04</v>
+        <v>313.41</v>
       </c>
       <c r="G94">
         <v>7.1</v>
@@ -8995,37 +8995,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M94">
-        <v>73.107432</v>
+        <v>73.902078</v>
       </c>
       <c r="N94">
-        <v>-50.15187644444445</v>
+        <v>-50.94652244444445</v>
       </c>
       <c r="O94">
-        <v>-10.03037528888889</v>
+        <v>-10.18930448888889</v>
       </c>
       <c r="P94">
-        <v>-40.12150115555556</v>
+        <v>-40.75721795555556</v>
       </c>
       <c r="Q94">
-        <v>-31.52150115555556</v>
+        <v>-32.15721795555557</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3093095260222439</v>
+        <v>0.3469537440254217</v>
       </c>
       <c r="T94">
-        <v>4.998678335847937</v>
+        <v>5.712775240969072</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06279951279250394</v>
+        <v>0.06212424921408991</v>
       </c>
       <c r="W94">
-        <v>0.2209918748835276</v>
+        <v>0.2211511020353176</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3139975639625197</v>
+        <v>0.3106212460704495</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2299572869746249</v>
+        <v>0.2318572869746249</v>
       </c>
       <c r="C95">
-        <v>-268.401735798051</v>
+        <v>-272.1588515254426</v>
       </c>
       <c r="D95">
-        <v>37.90826420194905</v>
+        <v>37.52114847455742</v>
       </c>
       <c r="E95">
-        <v>187.61</v>
+        <v>190.98</v>
       </c>
       <c r="F95">
-        <v>313.41</v>
+        <v>316.78</v>
       </c>
       <c r="G95">
         <v>7.1</v>
@@ -9077,37 +9077,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M95">
-        <v>73.902078</v>
+        <v>74.696724</v>
       </c>
       <c r="N95">
-        <v>-50.94652244444445</v>
+        <v>-51.74116844444445</v>
       </c>
       <c r="O95">
-        <v>-10.18930448888889</v>
+        <v>-10.34823368888889</v>
       </c>
       <c r="P95">
-        <v>-40.75721795555556</v>
+        <v>-41.39293475555556</v>
       </c>
       <c r="Q95">
-        <v>-32.15721795555557</v>
+        <v>-32.79293475555556</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3469537440254217</v>
+        <v>0.3971460346963254</v>
       </c>
       <c r="T95">
-        <v>5.712775240969072</v>
+        <v>6.664904447797252</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06212424921408991</v>
+        <v>0.06146335294585491</v>
       </c>
       <c r="W95">
-        <v>0.2211511020353176</v>
+        <v>0.2213069413753674</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3106212460704495</v>
+        <v>0.3073167647292745</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2318572869746249</v>
+        <v>0.2337572869746249</v>
       </c>
       <c r="C96">
-        <v>-272.1588515254426</v>
+        <v>-275.9081407950908</v>
       </c>
       <c r="D96">
-        <v>37.52114847455742</v>
+        <v>37.14185920490922</v>
       </c>
       <c r="E96">
-        <v>190.98</v>
+        <v>194.35</v>
       </c>
       <c r="F96">
-        <v>316.78</v>
+        <v>320.15</v>
       </c>
       <c r="G96">
         <v>7.1</v>
@@ -9159,37 +9159,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M96">
-        <v>74.696724</v>
+        <v>75.49137000000002</v>
       </c>
       <c r="N96">
-        <v>-51.74116844444445</v>
+        <v>-52.53581444444446</v>
       </c>
       <c r="O96">
-        <v>-10.34823368888889</v>
+        <v>-10.50716288888889</v>
       </c>
       <c r="P96">
-        <v>-41.39293475555556</v>
+        <v>-42.02865155555557</v>
       </c>
       <c r="Q96">
-        <v>-32.79293475555556</v>
+        <v>-33.42865155555558</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3971460346963254</v>
+        <v>0.4674152416355907</v>
       </c>
       <c r="T96">
-        <v>6.664904447797252</v>
+        <v>7.997885337356706</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06146335294585491</v>
+        <v>0.06081637028326695</v>
       </c>
       <c r="W96">
-        <v>0.2213069413753674</v>
+        <v>0.2214594998872057</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3073167647292745</v>
+        <v>0.3040818514163347</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2337572869746249</v>
+        <v>0.2356572869746249</v>
       </c>
       <c r="C97">
-        <v>-275.9081407950908</v>
+        <v>-279.6498385772189</v>
       </c>
       <c r="D97">
-        <v>37.14185920490922</v>
+        <v>36.77016142278114</v>
       </c>
       <c r="E97">
-        <v>194.35</v>
+        <v>197.72</v>
       </c>
       <c r="F97">
-        <v>320.15</v>
+        <v>323.52</v>
       </c>
       <c r="G97">
         <v>7.1</v>
@@ -9241,37 +9241,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M97">
-        <v>75.49137000000002</v>
+        <v>76.28601600000002</v>
       </c>
       <c r="N97">
-        <v>-52.53581444444446</v>
+        <v>-53.33046044444446</v>
       </c>
       <c r="O97">
-        <v>-10.50716288888889</v>
+        <v>-10.66609208888889</v>
       </c>
       <c r="P97">
-        <v>-42.02865155555557</v>
+        <v>-42.66436835555557</v>
       </c>
       <c r="Q97">
-        <v>-33.42865155555558</v>
+        <v>-34.06436835555557</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4674152416355907</v>
+        <v>0.5728190520444886</v>
       </c>
       <c r="T97">
-        <v>7.997885337356706</v>
+        <v>9.997356671695888</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06081637028326695</v>
+        <v>0.06018286642614959</v>
       </c>
       <c r="W97">
-        <v>0.2214594998872057</v>
+        <v>0.221608880096714</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3040818514163347</v>
+        <v>0.3009143321307479</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2356572869746249</v>
+        <v>0.2375572869746249</v>
       </c>
       <c r="C98">
-        <v>-279.6498385772189</v>
+        <v>-283.3841705293732</v>
       </c>
       <c r="D98">
-        <v>36.77016142278107</v>
+        <v>36.40582947062681</v>
       </c>
       <c r="E98">
-        <v>197.72</v>
+        <v>201.09</v>
       </c>
       <c r="F98">
-        <v>323.52</v>
+        <v>326.89</v>
       </c>
       <c r="G98">
         <v>7.1</v>
@@ -9323,37 +9323,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M98">
-        <v>76.286016</v>
+        <v>77.080662</v>
       </c>
       <c r="N98">
-        <v>-53.33046044444445</v>
+        <v>-54.12510644444445</v>
       </c>
       <c r="O98">
-        <v>-10.66609208888889</v>
+        <v>-10.82502128888889</v>
       </c>
       <c r="P98">
-        <v>-42.66436835555556</v>
+        <v>-43.30008515555556</v>
       </c>
       <c r="Q98">
-        <v>-34.06436835555556</v>
+        <v>-34.70008515555556</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.572819052044487</v>
+        <v>0.7484920693926495</v>
       </c>
       <c r="T98">
-        <v>9.99735667169586</v>
+        <v>13.32980889559448</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0601828664261496</v>
+        <v>0.05956242450423053</v>
       </c>
       <c r="W98">
-        <v>0.221608880096714</v>
+        <v>0.2217551803019024</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.300914332130748</v>
+        <v>0.2978121225211526</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2375572869746249</v>
+        <v>0.2394572869746249</v>
       </c>
       <c r="C99">
-        <v>-283.3841705293732</v>
+        <v>-287.1113534532632</v>
       </c>
       <c r="D99">
-        <v>36.40582947062681</v>
+        <v>36.04864654673678</v>
       </c>
       <c r="E99">
-        <v>201.09</v>
+        <v>204.46</v>
       </c>
       <c r="F99">
-        <v>326.89</v>
+        <v>330.26</v>
       </c>
       <c r="G99">
         <v>7.1</v>
@@ -9405,37 +9405,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M99">
-        <v>77.080662</v>
+        <v>77.875308</v>
       </c>
       <c r="N99">
-        <v>-54.12510644444445</v>
+        <v>-54.91975244444445</v>
       </c>
       <c r="O99">
-        <v>-10.82502128888889</v>
+        <v>-10.98395048888889</v>
       </c>
       <c r="P99">
-        <v>-43.30008515555556</v>
+        <v>-43.93580195555556</v>
       </c>
       <c r="Q99">
-        <v>-34.70008515555556</v>
+        <v>-35.33580195555557</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7484920693926495</v>
+        <v>1.099838104088974</v>
       </c>
       <c r="T99">
-        <v>13.32980889559448</v>
+        <v>19.99471334339172</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05956242450423053</v>
+        <v>0.05895464466235062</v>
       </c>
       <c r="W99">
-        <v>0.2217551803019024</v>
+        <v>0.2218984947886178</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2978121225211526</v>
+        <v>0.2947732233117532</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2394572869746249</v>
+        <v>0.2413572869746249</v>
       </c>
       <c r="C100">
-        <v>-287.1113534532632</v>
+        <v>-290.8315957249699</v>
       </c>
       <c r="D100">
-        <v>36.04864654673678</v>
+        <v>35.69840427503006</v>
       </c>
       <c r="E100">
-        <v>204.46</v>
+        <v>207.83</v>
       </c>
       <c r="F100">
-        <v>330.26</v>
+        <v>333.63</v>
       </c>
       <c r="G100">
         <v>7.1</v>
@@ -9487,37 +9487,37 @@
         <v>22.95555555555556</v>
       </c>
       <c r="M100">
-        <v>77.875308</v>
+        <v>78.669954</v>
       </c>
       <c r="N100">
-        <v>-54.91975244444445</v>
+        <v>-55.71439844444445</v>
       </c>
       <c r="O100">
-        <v>-10.98395048888889</v>
+        <v>-11.14287968888889</v>
       </c>
       <c r="P100">
-        <v>-43.93580195555556</v>
+        <v>-44.57151875555556</v>
       </c>
       <c r="Q100">
-        <v>-35.33580195555557</v>
+        <v>-35.97151875555556</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.099838104088974</v>
+        <v>2.153876208177948</v>
       </c>
       <c r="T100">
-        <v>19.99471334339172</v>
+        <v>39.98942668678344</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05895464466235062</v>
+        <v>0.05835914320111477</v>
       </c>
       <c r="W100">
-        <v>0.2218984947886178</v>
+        <v>0.2220389140331771</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2947732233117532</v>
+        <v>0.2917957160055737</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2413572869746249</v>
-      </c>
-      <c r="C101">
-        <v>-290.8315957249699</v>
-      </c>
-      <c r="D101">
-        <v>35.69840427503006</v>
-      </c>
-      <c r="E101">
-        <v>207.83</v>
-      </c>
-      <c r="F101">
-        <v>333.63</v>
-      </c>
-      <c r="G101">
-        <v>7.1</v>
-      </c>
-      <c r="H101">
-        <v>211.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>31.55555555555555</v>
-      </c>
-      <c r="K101">
-        <v>8.599999999999998</v>
-      </c>
-      <c r="L101">
-        <v>22.95555555555556</v>
-      </c>
-      <c r="M101">
-        <v>78.669954</v>
-      </c>
-      <c r="N101">
-        <v>-55.71439844444445</v>
-      </c>
-      <c r="O101">
-        <v>-11.14287968888889</v>
-      </c>
-      <c r="P101">
-        <v>-44.57151875555556</v>
-      </c>
-      <c r="Q101">
-        <v>-35.97151875555556</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.153876208177948</v>
-      </c>
-      <c r="T101">
-        <v>39.98942668678344</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05835914320111477</v>
-      </c>
-      <c r="W101">
-        <v>0.2220389140331771</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2917957160055737</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
